--- a/raw/Timetable_2026Autumn_2026BA.xlsx
+++ b/raw/Timetable_2026Autumn_2026BA.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30606"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88A76422-A42C-419A-8D90-9AB8769AB77E}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8765151-915C-4185-AD87-1421695652CE}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2918" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2918" uniqueCount="192">
   <si>
     <t>week</t>
   </si>
@@ -276,7 +276,10 @@
     <t>29       Sep.</t>
   </si>
   <si>
-    <t xml:space="preserve">B415 </t>
+    <t>B310</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B310 </t>
   </si>
   <si>
     <t>30       Sep.</t>
@@ -1110,6 +1113,51 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1146,24 +1194,6 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1180,33 +1210,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1566,81 +1569,81 @@
   <sheetData>
     <row r="1" spans="1:27" ht="13.9" customHeight="1"/>
     <row r="2" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="77" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="81"/>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="48" t="s">
+      <c r="E2" s="64"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="49"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="48" t="s">
+      <c r="H2" s="64"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="49"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="48" t="s">
+      <c r="K2" s="64"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="49"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="48" t="s">
+      <c r="N2" s="64"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="48" t="s">
+      <c r="Q2" s="64"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="49"/>
-      <c r="U2" s="50"/>
+      <c r="T2" s="64"/>
+      <c r="U2" s="65"/>
     </row>
     <row r="3" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="67"/>
+      <c r="A3" s="76"/>
       <c r="B3" s="82"/>
       <c r="C3" s="83"/>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="49"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="48" t="s">
+      <c r="E3" s="64"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="49"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="48" t="s">
+      <c r="H3" s="64"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="49"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="48" t="s">
+      <c r="K3" s="64"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="49"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="48" t="s">
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="50"/>
-      <c r="S3" s="48" t="s">
+      <c r="Q3" s="64"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="49"/>
-      <c r="U3" s="50"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="65"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="60">
+      <c r="A4" s="57">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -1694,7 +1697,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="61"/>
+      <c r="A5" s="58"/>
       <c r="B5" s="6" t="s">
         <v>24</v>
       </c>
@@ -1754,7 +1757,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="61"/>
+      <c r="A6" s="58"/>
       <c r="B6" s="6" t="s">
         <v>28</v>
       </c>
@@ -1814,7 +1817,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="61"/>
+      <c r="A7" s="58"/>
       <c r="B7" s="6" t="s">
         <v>33</v>
       </c>
@@ -1872,7 +1875,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="61"/>
+      <c r="A8" s="58"/>
       <c r="B8" s="6" t="s">
         <v>37</v>
       </c>
@@ -1930,7 +1933,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="61"/>
+      <c r="A9" s="58"/>
       <c r="B9" s="6" t="s">
         <v>42</v>
       </c>
@@ -1980,7 +1983,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="62"/>
+      <c r="A10" s="59"/>
       <c r="B10" s="6" t="s">
         <v>46</v>
       </c>
@@ -2024,7 +2027,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="63">
+      <c r="A11" s="60">
         <v>2</v>
       </c>
       <c r="B11" s="14" t="s">
@@ -2086,7 +2089,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="64"/>
+      <c r="A12" s="61"/>
       <c r="B12" s="14" t="s">
         <v>51</v>
       </c>
@@ -2144,7 +2147,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="64"/>
+      <c r="A13" s="61"/>
       <c r="B13" s="14" t="s">
         <v>52</v>
       </c>
@@ -2214,7 +2217,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="64"/>
+      <c r="A14" s="61"/>
       <c r="B14" s="14" t="s">
         <v>56</v>
       </c>
@@ -2262,7 +2265,7 @@
       <c r="AA14" s="7"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="64"/>
+      <c r="A15" s="61"/>
       <c r="B15" s="14" t="s">
         <v>57</v>
       </c>
@@ -2303,7 +2306,7 @@
       <c r="U15" s="17"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="64"/>
+      <c r="A16" s="61"/>
       <c r="B16" s="14" t="s">
         <v>58</v>
       </c>
@@ -2338,7 +2341,7 @@
       <c r="U16" s="17"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="65"/>
+      <c r="A17" s="62"/>
       <c r="B17" s="14" t="s">
         <v>59</v>
       </c>
@@ -2365,7 +2368,7 @@
       <c r="U17" s="17"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="60">
+      <c r="A18" s="57">
         <v>3</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -2410,7 +2413,7 @@
       <c r="U18" s="9"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="61"/>
+      <c r="A19" s="58"/>
       <c r="B19" s="6" t="s">
         <v>61</v>
       </c>
@@ -2453,7 +2456,7 @@
       <c r="U19" s="9"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="61"/>
+      <c r="A20" s="58"/>
       <c r="B20" s="6" t="s">
         <v>62</v>
       </c>
@@ -2508,7 +2511,7 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="61"/>
+      <c r="A21" s="58"/>
       <c r="B21" s="6" t="s">
         <v>63</v>
       </c>
@@ -2551,7 +2554,7 @@
       <c r="U21" s="9"/>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="61"/>
+      <c r="A22" s="58"/>
       <c r="B22" s="6" t="s">
         <v>64</v>
       </c>
@@ -2592,7 +2595,7 @@
       <c r="U22" s="9"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="61"/>
+      <c r="A23" s="58"/>
       <c r="B23" s="6" t="s">
         <v>65</v>
       </c>
@@ -2619,7 +2622,7 @@
       <c r="U23" s="9"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="62"/>
+      <c r="A24" s="59"/>
       <c r="B24" s="23" t="s">
         <v>66</v>
       </c>
@@ -2646,7 +2649,7 @@
       <c r="U24" s="26"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="63">
+      <c r="A25" s="60">
         <v>4</v>
       </c>
       <c r="B25" s="14" t="s">
@@ -2691,7 +2694,7 @@
       <c r="U25" s="17"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="64"/>
+      <c r="A26" s="61"/>
       <c r="B26" s="14" t="s">
         <v>68</v>
       </c>
@@ -2734,7 +2737,7 @@
       <c r="U26" s="17"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="64"/>
+      <c r="A27" s="61"/>
       <c r="B27" s="14" t="s">
         <v>69</v>
       </c>
@@ -2789,7 +2792,7 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="64"/>
+      <c r="A28" s="61"/>
       <c r="B28" s="14" t="s">
         <v>70</v>
       </c>
@@ -2832,90 +2835,90 @@
       <c r="U28" s="17"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="64"/>
+      <c r="A29" s="61"/>
       <c r="B29" s="27" t="s">
         <v>71</v>
       </c>
       <c r="C29" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D29" s="51" t="s">
+      <c r="D29" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="E29" s="52"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="52"/>
-      <c r="J29" s="52"/>
-      <c r="K29" s="52"/>
-      <c r="L29" s="52"/>
-      <c r="M29" s="52"/>
-      <c r="N29" s="52"/>
-      <c r="O29" s="52"/>
-      <c r="P29" s="52"/>
-      <c r="Q29" s="52"/>
-      <c r="R29" s="52"/>
-      <c r="S29" s="52"/>
-      <c r="T29" s="52"/>
-      <c r="U29" s="53"/>
+      <c r="E29" s="67"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="67"/>
+      <c r="J29" s="67"/>
+      <c r="K29" s="67"/>
+      <c r="L29" s="67"/>
+      <c r="M29" s="67"/>
+      <c r="N29" s="67"/>
+      <c r="O29" s="67"/>
+      <c r="P29" s="67"/>
+      <c r="Q29" s="67"/>
+      <c r="R29" s="67"/>
+      <c r="S29" s="67"/>
+      <c r="T29" s="67"/>
+      <c r="U29" s="68"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="64"/>
+      <c r="A30" s="61"/>
       <c r="B30" s="27" t="s">
         <v>73</v>
       </c>
       <c r="C30" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="54"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="55"/>
-      <c r="J30" s="55"/>
-      <c r="K30" s="55"/>
-      <c r="L30" s="55"/>
-      <c r="M30" s="55"/>
-      <c r="N30" s="55"/>
-      <c r="O30" s="55"/>
-      <c r="P30" s="55"/>
-      <c r="Q30" s="55"/>
-      <c r="R30" s="55"/>
-      <c r="S30" s="55"/>
-      <c r="T30" s="55"/>
-      <c r="U30" s="56"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="70"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="70"/>
+      <c r="M30" s="70"/>
+      <c r="N30" s="70"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="70"/>
+      <c r="Q30" s="70"/>
+      <c r="R30" s="70"/>
+      <c r="S30" s="70"/>
+      <c r="T30" s="70"/>
+      <c r="U30" s="71"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="65"/>
+      <c r="A31" s="62"/>
       <c r="B31" s="27" t="s">
         <v>74</v>
       </c>
       <c r="C31" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D31" s="57"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="58"/>
-      <c r="N31" s="58"/>
-      <c r="O31" s="58"/>
-      <c r="P31" s="58"/>
-      <c r="Q31" s="58"/>
-      <c r="R31" s="58"/>
-      <c r="S31" s="58"/>
-      <c r="T31" s="58"/>
-      <c r="U31" s="59"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73"/>
+      <c r="J31" s="73"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="73"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="73"/>
+      <c r="O31" s="73"/>
+      <c r="P31" s="73"/>
+      <c r="Q31" s="73"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="73"/>
+      <c r="T31" s="73"/>
+      <c r="U31" s="74"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="60">
+      <c r="A32" s="57">
         <v>5</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -2960,7 +2963,7 @@
       <c r="U32" s="9"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="61"/>
+      <c r="A33" s="58"/>
       <c r="B33" s="6" t="s">
         <v>77</v>
       </c>
@@ -2993,7 +2996,7 @@
         <v>50</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P33" s="6"/>
       <c r="Q33" s="8"/>
@@ -3003,9 +3006,9 @@
       <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="61"/>
+      <c r="A34" s="58"/>
       <c r="B34" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>29</v>
@@ -3046,202 +3049,202 @@
       <c r="U34" s="9"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="61"/>
+      <c r="A35" s="58"/>
       <c r="B35" s="29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="51" t="s">
+      <c r="D35" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="52"/>
-      <c r="N35" s="52"/>
-      <c r="O35" s="52"/>
-      <c r="P35" s="52"/>
-      <c r="Q35" s="52"/>
-      <c r="R35" s="52"/>
-      <c r="S35" s="52"/>
-      <c r="T35" s="52"/>
-      <c r="U35" s="53"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="67"/>
+      <c r="I35" s="67"/>
+      <c r="J35" s="67"/>
+      <c r="K35" s="67"/>
+      <c r="L35" s="67"/>
+      <c r="M35" s="67"/>
+      <c r="N35" s="67"/>
+      <c r="O35" s="67"/>
+      <c r="P35" s="67"/>
+      <c r="Q35" s="67"/>
+      <c r="R35" s="67"/>
+      <c r="S35" s="67"/>
+      <c r="T35" s="67"/>
+      <c r="U35" s="68"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="61"/>
+      <c r="A36" s="58"/>
       <c r="B36" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C36" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="54"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="55"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="55"/>
-      <c r="N36" s="55"/>
-      <c r="O36" s="55"/>
-      <c r="P36" s="55"/>
-      <c r="Q36" s="55"/>
-      <c r="R36" s="55"/>
-      <c r="S36" s="55"/>
-      <c r="T36" s="55"/>
-      <c r="U36" s="56"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="70"/>
+      <c r="K36" s="70"/>
+      <c r="L36" s="70"/>
+      <c r="M36" s="70"/>
+      <c r="N36" s="70"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="70"/>
+      <c r="Q36" s="70"/>
+      <c r="R36" s="70"/>
+      <c r="S36" s="70"/>
+      <c r="T36" s="70"/>
+      <c r="U36" s="71"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="61"/>
+      <c r="A37" s="58"/>
       <c r="B37" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C37" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="D37" s="54"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="55"/>
-      <c r="J37" s="55"/>
-      <c r="K37" s="55"/>
-      <c r="L37" s="55"/>
-      <c r="M37" s="55"/>
-      <c r="N37" s="55"/>
-      <c r="O37" s="55"/>
-      <c r="P37" s="55"/>
-      <c r="Q37" s="55"/>
-      <c r="R37" s="55"/>
-      <c r="S37" s="55"/>
-      <c r="T37" s="55"/>
-      <c r="U37" s="56"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="70"/>
+      <c r="H37" s="70"/>
+      <c r="I37" s="70"/>
+      <c r="J37" s="70"/>
+      <c r="K37" s="70"/>
+      <c r="L37" s="70"/>
+      <c r="M37" s="70"/>
+      <c r="N37" s="70"/>
+      <c r="O37" s="70"/>
+      <c r="P37" s="70"/>
+      <c r="Q37" s="70"/>
+      <c r="R37" s="70"/>
+      <c r="S37" s="70"/>
+      <c r="T37" s="70"/>
+      <c r="U37" s="71"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="62"/>
+      <c r="A38" s="59"/>
       <c r="B38" s="29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C38" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D38" s="54"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="55"/>
-      <c r="J38" s="55"/>
-      <c r="K38" s="55"/>
-      <c r="L38" s="55"/>
-      <c r="M38" s="55"/>
-      <c r="N38" s="55"/>
-      <c r="O38" s="55"/>
-      <c r="P38" s="55"/>
-      <c r="Q38" s="55"/>
-      <c r="R38" s="55"/>
-      <c r="S38" s="55"/>
-      <c r="T38" s="55"/>
-      <c r="U38" s="56"/>
+      <c r="D38" s="69"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="70"/>
+      <c r="Q38" s="70"/>
+      <c r="R38" s="70"/>
+      <c r="S38" s="70"/>
+      <c r="T38" s="70"/>
+      <c r="U38" s="71"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="63">
+      <c r="A39" s="60">
         <v>6</v>
       </c>
       <c r="B39" s="29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C39" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="54"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="55"/>
-      <c r="I39" s="55"/>
-      <c r="J39" s="55"/>
-      <c r="K39" s="55"/>
-      <c r="L39" s="55"/>
-      <c r="M39" s="55"/>
-      <c r="N39" s="55"/>
-      <c r="O39" s="55"/>
-      <c r="P39" s="55"/>
-      <c r="Q39" s="55"/>
-      <c r="R39" s="55"/>
-      <c r="S39" s="55"/>
-      <c r="T39" s="55"/>
-      <c r="U39" s="56"/>
+      <c r="D39" s="69"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="70"/>
+      <c r="M39" s="70"/>
+      <c r="N39" s="70"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="70"/>
+      <c r="Q39" s="70"/>
+      <c r="R39" s="70"/>
+      <c r="S39" s="70"/>
+      <c r="T39" s="70"/>
+      <c r="U39" s="71"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="64"/>
+      <c r="A40" s="61"/>
       <c r="B40" s="29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C40" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="54"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="55"/>
-      <c r="J40" s="55"/>
-      <c r="K40" s="55"/>
-      <c r="L40" s="55"/>
-      <c r="M40" s="55"/>
-      <c r="N40" s="55"/>
-      <c r="O40" s="55"/>
-      <c r="P40" s="55"/>
-      <c r="Q40" s="55"/>
-      <c r="R40" s="55"/>
-      <c r="S40" s="55"/>
-      <c r="T40" s="55"/>
-      <c r="U40" s="56"/>
+      <c r="D40" s="69"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="70"/>
+      <c r="M40" s="70"/>
+      <c r="N40" s="70"/>
+      <c r="O40" s="70"/>
+      <c r="P40" s="70"/>
+      <c r="Q40" s="70"/>
+      <c r="R40" s="70"/>
+      <c r="S40" s="70"/>
+      <c r="T40" s="70"/>
+      <c r="U40" s="71"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="64"/>
+      <c r="A41" s="61"/>
       <c r="B41" s="29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C41" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="D41" s="57"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="58"/>
-      <c r="N41" s="58"/>
-      <c r="O41" s="58"/>
-      <c r="P41" s="58"/>
-      <c r="Q41" s="58"/>
-      <c r="R41" s="58"/>
-      <c r="S41" s="58"/>
-      <c r="T41" s="58"/>
-      <c r="U41" s="59"/>
+      <c r="D41" s="72"/>
+      <c r="E41" s="73"/>
+      <c r="F41" s="73"/>
+      <c r="G41" s="73"/>
+      <c r="H41" s="73"/>
+      <c r="I41" s="73"/>
+      <c r="J41" s="73"/>
+      <c r="K41" s="73"/>
+      <c r="L41" s="73"/>
+      <c r="M41" s="73"/>
+      <c r="N41" s="73"/>
+      <c r="O41" s="73"/>
+      <c r="P41" s="73"/>
+      <c r="Q41" s="73"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="73"/>
+      <c r="T41" s="73"/>
+      <c r="U41" s="74"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="64"/>
+      <c r="A42" s="61"/>
       <c r="B42" s="30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>34</v>
@@ -3282,9 +3285,9 @@
       <c r="U42" s="17"/>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="64"/>
+      <c r="A43" s="61"/>
       <c r="B43" s="30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>38</v>
@@ -3323,9 +3326,9 @@
       <c r="U43" s="17"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="64"/>
+      <c r="A44" s="61"/>
       <c r="B44" s="31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C44" s="24" t="s">
         <v>43</v>
@@ -3350,9 +3353,9 @@
       <c r="U44" s="26"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="65"/>
+      <c r="A45" s="62"/>
       <c r="B45" s="30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>47</v>
@@ -3377,11 +3380,11 @@
       <c r="U45" s="17"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="60">
+      <c r="A46" s="57">
         <v>7</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>15</v>
@@ -3422,9 +3425,9 @@
       <c r="U46" s="9"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="61"/>
+      <c r="A47" s="58"/>
       <c r="B47" s="22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>25</v>
@@ -3446,7 +3449,7 @@
         <v>50</v>
       </c>
       <c r="L47" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>49</v>
@@ -3455,7 +3458,7 @@
         <v>50</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P47" s="6"/>
       <c r="Q47" s="8"/>
@@ -3465,9 +3468,9 @@
       <c r="U47" s="9"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="61"/>
+      <c r="A48" s="58"/>
       <c r="B48" s="22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>29</v>
@@ -3508,9 +3511,9 @@
       <c r="U48" s="9"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="61"/>
+      <c r="A49" s="58"/>
       <c r="B49" s="22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>34</v>
@@ -3551,9 +3554,9 @@
       <c r="U49" s="9"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="61"/>
+      <c r="A50" s="58"/>
       <c r="B50" s="22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>38</v>
@@ -3592,9 +3595,9 @@
       <c r="U50" s="9"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="61"/>
+      <c r="A51" s="58"/>
       <c r="B51" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>43</v>
@@ -3627,9 +3630,9 @@
       <c r="U51" s="9"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="62"/>
+      <c r="A52" s="59"/>
       <c r="B52" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>47</v>
@@ -3654,11 +3657,11 @@
       <c r="U52" s="9"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="63">
+      <c r="A53" s="60">
         <v>8</v>
       </c>
       <c r="B53" s="30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C53" s="15" t="s">
         <v>15</v>
@@ -3699,9 +3702,9 @@
       <c r="U53" s="17"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="64"/>
+      <c r="A54" s="61"/>
       <c r="B54" s="30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C54" s="15" t="s">
         <v>25</v>
@@ -3723,7 +3726,7 @@
         <v>50</v>
       </c>
       <c r="L54" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M54" s="14" t="s">
         <v>49</v>
@@ -3732,7 +3735,7 @@
         <v>50</v>
       </c>
       <c r="O54" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P54" s="14"/>
       <c r="Q54" s="16"/>
@@ -3742,9 +3745,9 @@
       <c r="U54" s="17"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="64"/>
+      <c r="A55" s="61"/>
       <c r="B55" s="30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C55" s="15" t="s">
         <v>29</v>
@@ -3797,9 +3800,9 @@
       </c>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="64"/>
+      <c r="A56" s="61"/>
       <c r="B56" s="30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C56" s="15" t="s">
         <v>34</v>
@@ -3840,9 +3843,9 @@
       <c r="U56" s="17"/>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="64"/>
+      <c r="A57" s="61"/>
       <c r="B57" s="30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C57" s="15" t="s">
         <v>38</v>
@@ -3883,9 +3886,9 @@
       <c r="U57" s="17"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="64"/>
+      <c r="A58" s="61"/>
       <c r="B58" s="30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>43</v>
@@ -3918,9 +3921,9 @@
       <c r="U58" s="17"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="65"/>
+      <c r="A59" s="62"/>
       <c r="B59" s="30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>47</v>
@@ -3945,11 +3948,11 @@
       <c r="U59" s="17"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="60">
+      <c r="A60" s="57">
         <v>9</v>
       </c>
       <c r="B60" s="22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>15</v>
@@ -3978,9 +3981,9 @@
       <c r="U60" s="9"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="61"/>
+      <c r="A61" s="58"/>
       <c r="B61" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>25</v>
@@ -4002,7 +4005,7 @@
         <v>50</v>
       </c>
       <c r="L61" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>49</v>
@@ -4011,7 +4014,7 @@
         <v>50</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P61" s="6"/>
       <c r="Q61" s="8"/>
@@ -4021,9 +4024,9 @@
       <c r="U61" s="9"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="61"/>
+      <c r="A62" s="58"/>
       <c r="B62" s="22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>29</v>
@@ -4076,9 +4079,9 @@
       </c>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="61"/>
+      <c r="A63" s="58"/>
       <c r="B63" s="22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>34</v>
@@ -4119,9 +4122,9 @@
       <c r="U63" s="32"/>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="61"/>
+      <c r="A64" s="58"/>
       <c r="B64" s="22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>38</v>
@@ -4162,9 +4165,9 @@
       <c r="U64" s="32"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="61"/>
+      <c r="A65" s="58"/>
       <c r="B65" s="22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>43</v>
@@ -4197,9 +4200,9 @@
       <c r="U65" s="32"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="62"/>
+      <c r="A66" s="59"/>
       <c r="B66" s="22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>47</v>
@@ -4224,11 +4227,11 @@
       <c r="U66" s="32"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="63">
+      <c r="A67" s="60">
         <v>10</v>
       </c>
       <c r="B67" s="30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>15</v>
@@ -4257,9 +4260,9 @@
       <c r="U67" s="33"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="64"/>
+      <c r="A68" s="61"/>
       <c r="B68" s="30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C68" s="15" t="s">
         <v>25</v>
@@ -4281,7 +4284,7 @@
         <v>50</v>
       </c>
       <c r="L68" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M68" s="14" t="s">
         <v>49</v>
@@ -4290,7 +4293,7 @@
         <v>50</v>
       </c>
       <c r="O68" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P68" s="14"/>
       <c r="Q68" s="16"/>
@@ -4300,9 +4303,9 @@
       <c r="U68" s="33"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="64"/>
+      <c r="A69" s="61"/>
       <c r="B69" s="30" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C69" s="15" t="s">
         <v>29</v>
@@ -4343,9 +4346,9 @@
       <c r="U69" s="33"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="64"/>
+      <c r="A70" s="61"/>
       <c r="B70" s="30" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C70" s="15" t="s">
         <v>34</v>
@@ -4386,9 +4389,9 @@
       <c r="U70" s="33"/>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="64"/>
+      <c r="A71" s="61"/>
       <c r="B71" s="30" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>38</v>
@@ -4429,9 +4432,9 @@
       <c r="U71" s="33"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="64"/>
+      <c r="A72" s="61"/>
       <c r="B72" s="30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>43</v>
@@ -4456,9 +4459,9 @@
       <c r="U72" s="33"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="65"/>
+      <c r="A73" s="62"/>
       <c r="B73" s="30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C73" s="15" t="s">
         <v>47</v>
@@ -4483,11 +4486,11 @@
       <c r="U73" s="33"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="60">
+      <c r="A74" s="57">
         <v>11</v>
       </c>
       <c r="B74" s="22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>15</v>
@@ -4516,9 +4519,9 @@
       <c r="U74" s="32"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="61"/>
+      <c r="A75" s="58"/>
       <c r="B75" s="22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C75" s="7" t="s">
         <v>25</v>
@@ -4540,7 +4543,7 @@
         <v>50</v>
       </c>
       <c r="L75" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>49</v>
@@ -4549,7 +4552,7 @@
         <v>50</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P75" s="6"/>
       <c r="Q75" s="8"/>
@@ -4559,9 +4562,9 @@
       <c r="U75" s="32"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="61"/>
+      <c r="A76" s="58"/>
       <c r="B76" s="22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C76" s="7" t="s">
         <v>29</v>
@@ -4614,9 +4617,9 @@
       </c>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="61"/>
+      <c r="A77" s="58"/>
       <c r="B77" s="22" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C77" s="7" t="s">
         <v>34</v>
@@ -4657,9 +4660,9 @@
       <c r="U77" s="9"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="61"/>
+      <c r="A78" s="58"/>
       <c r="B78" s="22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>38</v>
@@ -4700,9 +4703,9 @@
       <c r="U78" s="9"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="61"/>
+      <c r="A79" s="58"/>
       <c r="B79" s="22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C79" s="7" t="s">
         <v>43</v>
@@ -4727,9 +4730,9 @@
       <c r="U79" s="9"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="62"/>
+      <c r="A80" s="59"/>
       <c r="B80" s="22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C80" s="7" t="s">
         <v>47</v>
@@ -4754,11 +4757,11 @@
       <c r="U80" s="9"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="63">
+      <c r="A81" s="60">
         <v>12</v>
       </c>
       <c r="B81" s="30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C81" s="15" t="s">
         <v>15</v>
@@ -4787,9 +4790,9 @@
       <c r="U81" s="17"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="64"/>
+      <c r="A82" s="61"/>
       <c r="B82" s="30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>25</v>
@@ -4811,7 +4814,7 @@
         <v>50</v>
       </c>
       <c r="L82" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M82" s="14" t="s">
         <v>49</v>
@@ -4820,7 +4823,7 @@
         <v>50</v>
       </c>
       <c r="O82" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P82" s="14"/>
       <c r="Q82" s="16"/>
@@ -4830,9 +4833,9 @@
       <c r="U82" s="17"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="64"/>
+      <c r="A83" s="61"/>
       <c r="B83" s="30" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>29</v>
@@ -4866,28 +4869,28 @@
       <c r="N83" s="16"/>
       <c r="O83" s="17"/>
       <c r="P83" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q83" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R83" s="17" t="s">
         <v>55</v>
       </c>
       <c r="S83" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T83" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U83" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="64"/>
+      <c r="A84" s="61"/>
       <c r="B84" s="30" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>34</v>
@@ -4928,9 +4931,9 @@
       <c r="U84" s="17"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="64"/>
+      <c r="A85" s="61"/>
       <c r="B85" s="30" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C85" s="15" t="s">
         <v>38</v>
@@ -4971,9 +4974,9 @@
       <c r="U85" s="17"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="64"/>
+      <c r="A86" s="61"/>
       <c r="B86" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C86" s="15" t="s">
         <v>43</v>
@@ -5006,9 +5009,9 @@
       <c r="U86" s="17"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="65"/>
+      <c r="A87" s="62"/>
       <c r="B87" s="30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>47</v>
@@ -5033,11 +5036,11 @@
       <c r="U87" s="17"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="60">
+      <c r="A88" s="57">
         <v>13</v>
       </c>
       <c r="B88" s="22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>15</v>
@@ -5066,9 +5069,9 @@
       <c r="U88" s="9"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="61"/>
+      <c r="A89" s="58"/>
       <c r="B89" s="22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C89" s="7" t="s">
         <v>25</v>
@@ -5090,7 +5093,7 @@
         <v>50</v>
       </c>
       <c r="L89" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M89" s="6" t="s">
         <v>49</v>
@@ -5099,7 +5102,7 @@
         <v>50</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P89" s="6"/>
       <c r="Q89" s="8"/>
@@ -5109,9 +5112,9 @@
       <c r="U89" s="9"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="61"/>
+      <c r="A90" s="58"/>
       <c r="B90" s="22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C90" s="7" t="s">
         <v>29</v>
@@ -5145,28 +5148,28 @@
       <c r="N90" s="8"/>
       <c r="O90" s="9"/>
       <c r="P90" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q90" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R90" s="9" t="s">
         <v>55</v>
       </c>
       <c r="S90" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T90" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U90" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="61"/>
+      <c r="A91" s="58"/>
       <c r="B91" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C91" s="7" t="s">
         <v>34</v>
@@ -5207,9 +5210,9 @@
       <c r="U91" s="9"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="61"/>
+      <c r="A92" s="58"/>
       <c r="B92" s="22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C92" s="7" t="s">
         <v>38</v>
@@ -5250,9 +5253,9 @@
       <c r="U92" s="9"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="61"/>
+      <c r="A93" s="58"/>
       <c r="B93" s="22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C93" s="7" t="s">
         <v>43</v>
@@ -5285,9 +5288,9 @@
       <c r="U93" s="9"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="62"/>
+      <c r="A94" s="59"/>
       <c r="B94" s="22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C94" s="7" t="s">
         <v>47</v>
@@ -5312,11 +5315,11 @@
       <c r="U94" s="9"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="63">
+      <c r="A95" s="60">
         <v>14</v>
       </c>
       <c r="B95" s="30" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C95" s="15" t="s">
         <v>15</v>
@@ -5345,9 +5348,9 @@
       <c r="U95" s="17"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="64"/>
+      <c r="A96" s="61"/>
       <c r="B96" s="30" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C96" s="15" t="s">
         <v>25</v>
@@ -5369,7 +5372,7 @@
         <v>50</v>
       </c>
       <c r="L96" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M96" s="14" t="s">
         <v>49</v>
@@ -5378,7 +5381,7 @@
         <v>50</v>
       </c>
       <c r="O96" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P96" s="14"/>
       <c r="Q96" s="16"/>
@@ -5388,9 +5391,9 @@
       <c r="U96" s="17"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="64"/>
+      <c r="A97" s="61"/>
       <c r="B97" s="30" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C97" s="15" t="s">
         <v>29</v>
@@ -5424,28 +5427,28 @@
       <c r="N97" s="16"/>
       <c r="O97" s="17"/>
       <c r="P97" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q97" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R97" s="17" t="s">
         <v>55</v>
       </c>
       <c r="S97" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T97" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U97" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="64"/>
+      <c r="A98" s="61"/>
       <c r="B98" s="30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C98" s="15" t="s">
         <v>34</v>
@@ -5486,9 +5489,9 @@
       <c r="U98" s="17"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="64"/>
+      <c r="A99" s="61"/>
       <c r="B99" s="30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C99" s="15" t="s">
         <v>38</v>
@@ -5529,9 +5532,9 @@
       <c r="U99" s="17"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="64"/>
+      <c r="A100" s="61"/>
       <c r="B100" s="30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C100" s="15" t="s">
         <v>43</v>
@@ -5556,9 +5559,9 @@
       <c r="U100" s="17"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="65"/>
+      <c r="A101" s="62"/>
       <c r="B101" s="30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C101" s="15" t="s">
         <v>47</v>
@@ -5583,11 +5586,11 @@
       <c r="U101" s="17"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="60">
+      <c r="A102" s="57">
         <v>15</v>
       </c>
       <c r="B102" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C102" s="7" t="s">
         <v>15</v>
@@ -5616,9 +5619,9 @@
       <c r="U102" s="9"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="61"/>
+      <c r="A103" s="58"/>
       <c r="B103" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>25</v>
@@ -5640,7 +5643,7 @@
         <v>50</v>
       </c>
       <c r="L103" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M103" s="6" t="s">
         <v>49</v>
@@ -5649,7 +5652,7 @@
         <v>50</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P103" s="6"/>
       <c r="Q103" s="8"/>
@@ -5659,9 +5662,9 @@
       <c r="U103" s="9"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="61"/>
+      <c r="A104" s="58"/>
       <c r="B104" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C104" s="7" t="s">
         <v>29</v>
@@ -5695,28 +5698,28 @@
       <c r="N104" s="8"/>
       <c r="O104" s="9"/>
       <c r="P104" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q104" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R104" s="9" t="s">
         <v>55</v>
       </c>
       <c r="S104" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T104" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U104" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="61"/>
+      <c r="A105" s="58"/>
       <c r="B105" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>34</v>
@@ -5757,9 +5760,9 @@
       <c r="U105" s="9"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="61"/>
+      <c r="A106" s="58"/>
       <c r="B106" s="22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C106" s="7" t="s">
         <v>38</v>
@@ -5800,9 +5803,9 @@
       <c r="U106" s="9"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="61"/>
+      <c r="A107" s="58"/>
       <c r="B107" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C107" s="7" t="s">
         <v>43</v>
@@ -5835,9 +5838,9 @@
       <c r="U107" s="9"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="62"/>
+      <c r="A108" s="59"/>
       <c r="B108" s="22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C108" s="7" t="s">
         <v>47</v>
@@ -5862,11 +5865,11 @@
       <c r="U108" s="9"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="63">
+      <c r="A109" s="60">
         <v>16</v>
       </c>
       <c r="B109" s="30" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C109" s="15" t="s">
         <v>15</v>
@@ -5895,9 +5898,9 @@
       <c r="U109" s="33"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="64"/>
+      <c r="A110" s="61"/>
       <c r="B110" s="30" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C110" s="15" t="s">
         <v>25</v>
@@ -5919,7 +5922,7 @@
         <v>50</v>
       </c>
       <c r="L110" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M110" s="14" t="s">
         <v>49</v>
@@ -5928,7 +5931,7 @@
         <v>50</v>
       </c>
       <c r="O110" s="17" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P110" s="14"/>
       <c r="Q110" s="16"/>
@@ -5938,9 +5941,9 @@
       <c r="U110" s="33"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="64"/>
+      <c r="A111" s="61"/>
       <c r="B111" s="30" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C111" s="15" t="s">
         <v>29</v>
@@ -5974,28 +5977,28 @@
       <c r="N111" s="16"/>
       <c r="O111" s="17"/>
       <c r="P111" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q111" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R111" s="17" t="s">
         <v>55</v>
       </c>
       <c r="S111" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T111" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U111" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="64"/>
+      <c r="A112" s="61"/>
       <c r="B112" s="30" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C112" s="15" t="s">
         <v>34</v>
@@ -6036,9 +6039,9 @@
       <c r="U112" s="33"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="64"/>
+      <c r="A113" s="61"/>
       <c r="B113" s="30" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C113" s="15" t="s">
         <v>38</v>
@@ -6079,9 +6082,9 @@
       <c r="U113" s="33"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="64"/>
+      <c r="A114" s="61"/>
       <c r="B114" s="30" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C114" s="15" t="s">
         <v>43</v>
@@ -6106,9 +6109,9 @@
       <c r="U114" s="33"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="65"/>
+      <c r="A115" s="62"/>
       <c r="B115" s="30" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C115" s="15" t="s">
         <v>47</v>
@@ -6133,11 +6136,11 @@
       <c r="U115" s="33"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="60">
+      <c r="A116" s="57">
         <v>17</v>
       </c>
       <c r="B116" s="22" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C116" s="7" t="s">
         <v>15</v>
@@ -6164,9 +6167,9 @@
       <c r="U116" s="9"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="61"/>
+      <c r="A117" s="58"/>
       <c r="B117" s="22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>25</v>
@@ -6186,7 +6189,7 @@
         <v>50</v>
       </c>
       <c r="L117" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M117" s="6" t="s">
         <v>49</v>
@@ -6195,7 +6198,7 @@
         <v>50</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P117" s="6"/>
       <c r="Q117" s="8"/>
@@ -6205,9 +6208,9 @@
       <c r="U117" s="9"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="61"/>
+      <c r="A118" s="58"/>
       <c r="B118" s="22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C118" s="7" t="s">
         <v>29</v>
@@ -6239,28 +6242,28 @@
       <c r="N118" s="8"/>
       <c r="O118" s="9"/>
       <c r="P118" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q118" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R118" s="9" t="s">
         <v>55</v>
       </c>
       <c r="S118" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T118" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U118" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="61"/>
+      <c r="A119" s="58"/>
       <c r="B119" s="22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>34</v>
@@ -6299,9 +6302,9 @@
       <c r="U119" s="9"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="61"/>
+      <c r="A120" s="58"/>
       <c r="B120" s="22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C120" s="7" t="s">
         <v>38</v>
@@ -6342,9 +6345,9 @@
       <c r="U120" s="9"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="61"/>
+      <c r="A121" s="58"/>
       <c r="B121" s="22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>43</v>
@@ -6369,9 +6372,9 @@
       <c r="U121" s="9"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="62"/>
+      <c r="A122" s="59"/>
       <c r="B122" s="22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>47</v>
@@ -6396,388 +6399,388 @@
       <c r="U122" s="9"/>
     </row>
     <row r="123" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="63">
+      <c r="A123" s="60">
         <v>18</v>
       </c>
       <c r="B123" s="30" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C123" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D123" s="72" t="s">
-        <v>171</v>
-      </c>
-      <c r="E123" s="73"/>
-      <c r="F123" s="73"/>
-      <c r="G123" s="73"/>
-      <c r="H123" s="73"/>
-      <c r="I123" s="73"/>
-      <c r="J123" s="73"/>
-      <c r="K123" s="73"/>
-      <c r="L123" s="73"/>
-      <c r="M123" s="73"/>
-      <c r="N123" s="73"/>
-      <c r="O123" s="73"/>
-      <c r="P123" s="73"/>
-      <c r="Q123" s="73"/>
-      <c r="R123" s="73"/>
-      <c r="S123" s="73"/>
-      <c r="T123" s="73"/>
-      <c r="U123" s="74"/>
+      <c r="D123" s="48" t="s">
+        <v>172</v>
+      </c>
+      <c r="E123" s="49"/>
+      <c r="F123" s="49"/>
+      <c r="G123" s="49"/>
+      <c r="H123" s="49"/>
+      <c r="I123" s="49"/>
+      <c r="J123" s="49"/>
+      <c r="K123" s="49"/>
+      <c r="L123" s="49"/>
+      <c r="M123" s="49"/>
+      <c r="N123" s="49"/>
+      <c r="O123" s="49"/>
+      <c r="P123" s="49"/>
+      <c r="Q123" s="49"/>
+      <c r="R123" s="49"/>
+      <c r="S123" s="49"/>
+      <c r="T123" s="49"/>
+      <c r="U123" s="50"/>
     </row>
     <row r="124" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="64"/>
+      <c r="A124" s="61"/>
       <c r="B124" s="30" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C124" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D124" s="75"/>
-      <c r="E124" s="76"/>
-      <c r="F124" s="76"/>
-      <c r="G124" s="76"/>
-      <c r="H124" s="76"/>
-      <c r="I124" s="76"/>
-      <c r="J124" s="76"/>
-      <c r="K124" s="76"/>
-      <c r="L124" s="76"/>
-      <c r="M124" s="76"/>
-      <c r="N124" s="76"/>
-      <c r="O124" s="76"/>
-      <c r="P124" s="76"/>
-      <c r="Q124" s="76"/>
-      <c r="R124" s="76"/>
-      <c r="S124" s="76"/>
-      <c r="T124" s="76"/>
-      <c r="U124" s="77"/>
+      <c r="D124" s="51"/>
+      <c r="E124" s="52"/>
+      <c r="F124" s="52"/>
+      <c r="G124" s="52"/>
+      <c r="H124" s="52"/>
+      <c r="I124" s="52"/>
+      <c r="J124" s="52"/>
+      <c r="K124" s="52"/>
+      <c r="L124" s="52"/>
+      <c r="M124" s="52"/>
+      <c r="N124" s="52"/>
+      <c r="O124" s="52"/>
+      <c r="P124" s="52"/>
+      <c r="Q124" s="52"/>
+      <c r="R124" s="52"/>
+      <c r="S124" s="52"/>
+      <c r="T124" s="52"/>
+      <c r="U124" s="53"/>
     </row>
     <row r="125" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="64"/>
+      <c r="A125" s="61"/>
       <c r="B125" s="30" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C125" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D125" s="75"/>
-      <c r="E125" s="76"/>
-      <c r="F125" s="76"/>
-      <c r="G125" s="76"/>
-      <c r="H125" s="76"/>
-      <c r="I125" s="76"/>
-      <c r="J125" s="76"/>
-      <c r="K125" s="76"/>
-      <c r="L125" s="76"/>
-      <c r="M125" s="76"/>
-      <c r="N125" s="76"/>
-      <c r="O125" s="76"/>
-      <c r="P125" s="76"/>
-      <c r="Q125" s="76"/>
-      <c r="R125" s="76"/>
-      <c r="S125" s="76"/>
-      <c r="T125" s="76"/>
-      <c r="U125" s="77"/>
+      <c r="D125" s="51"/>
+      <c r="E125" s="52"/>
+      <c r="F125" s="52"/>
+      <c r="G125" s="52"/>
+      <c r="H125" s="52"/>
+      <c r="I125" s="52"/>
+      <c r="J125" s="52"/>
+      <c r="K125" s="52"/>
+      <c r="L125" s="52"/>
+      <c r="M125" s="52"/>
+      <c r="N125" s="52"/>
+      <c r="O125" s="52"/>
+      <c r="P125" s="52"/>
+      <c r="Q125" s="52"/>
+      <c r="R125" s="52"/>
+      <c r="S125" s="52"/>
+      <c r="T125" s="52"/>
+      <c r="U125" s="53"/>
     </row>
     <row r="126" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="64"/>
+      <c r="A126" s="61"/>
       <c r="B126" s="30" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C126" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D126" s="75"/>
-      <c r="E126" s="76"/>
-      <c r="F126" s="76"/>
-      <c r="G126" s="76"/>
-      <c r="H126" s="76"/>
-      <c r="I126" s="76"/>
-      <c r="J126" s="76"/>
-      <c r="K126" s="76"/>
-      <c r="L126" s="76"/>
-      <c r="M126" s="76"/>
-      <c r="N126" s="76"/>
-      <c r="O126" s="76"/>
-      <c r="P126" s="76"/>
-      <c r="Q126" s="76"/>
-      <c r="R126" s="76"/>
-      <c r="S126" s="76"/>
-      <c r="T126" s="76"/>
-      <c r="U126" s="77"/>
+      <c r="D126" s="51"/>
+      <c r="E126" s="52"/>
+      <c r="F126" s="52"/>
+      <c r="G126" s="52"/>
+      <c r="H126" s="52"/>
+      <c r="I126" s="52"/>
+      <c r="J126" s="52"/>
+      <c r="K126" s="52"/>
+      <c r="L126" s="52"/>
+      <c r="M126" s="52"/>
+      <c r="N126" s="52"/>
+      <c r="O126" s="52"/>
+      <c r="P126" s="52"/>
+      <c r="Q126" s="52"/>
+      <c r="R126" s="52"/>
+      <c r="S126" s="52"/>
+      <c r="T126" s="52"/>
+      <c r="U126" s="53"/>
     </row>
     <row r="127" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="64"/>
+      <c r="A127" s="61"/>
       <c r="B127" s="29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C127" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D127" s="75"/>
-      <c r="E127" s="76"/>
-      <c r="F127" s="76"/>
-      <c r="G127" s="76"/>
-      <c r="H127" s="76"/>
-      <c r="I127" s="76"/>
-      <c r="J127" s="76"/>
-      <c r="K127" s="76"/>
-      <c r="L127" s="76"/>
-      <c r="M127" s="76"/>
-      <c r="N127" s="76"/>
-      <c r="O127" s="76"/>
-      <c r="P127" s="76"/>
-      <c r="Q127" s="76"/>
-      <c r="R127" s="76"/>
-      <c r="S127" s="76"/>
-      <c r="T127" s="76"/>
-      <c r="U127" s="77"/>
+      <c r="D127" s="51"/>
+      <c r="E127" s="52"/>
+      <c r="F127" s="52"/>
+      <c r="G127" s="52"/>
+      <c r="H127" s="52"/>
+      <c r="I127" s="52"/>
+      <c r="J127" s="52"/>
+      <c r="K127" s="52"/>
+      <c r="L127" s="52"/>
+      <c r="M127" s="52"/>
+      <c r="N127" s="52"/>
+      <c r="O127" s="52"/>
+      <c r="P127" s="52"/>
+      <c r="Q127" s="52"/>
+      <c r="R127" s="52"/>
+      <c r="S127" s="52"/>
+      <c r="T127" s="52"/>
+      <c r="U127" s="53"/>
     </row>
     <row r="128" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="64"/>
+      <c r="A128" s="61"/>
       <c r="B128" s="30" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C128" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D128" s="75"/>
-      <c r="E128" s="76"/>
-      <c r="F128" s="76"/>
-      <c r="G128" s="76"/>
-      <c r="H128" s="76"/>
-      <c r="I128" s="76"/>
-      <c r="J128" s="76"/>
-      <c r="K128" s="76"/>
-      <c r="L128" s="76"/>
-      <c r="M128" s="76"/>
-      <c r="N128" s="76"/>
-      <c r="O128" s="76"/>
-      <c r="P128" s="76"/>
-      <c r="Q128" s="76"/>
-      <c r="R128" s="76"/>
-      <c r="S128" s="76"/>
-      <c r="T128" s="76"/>
-      <c r="U128" s="77"/>
+      <c r="D128" s="51"/>
+      <c r="E128" s="52"/>
+      <c r="F128" s="52"/>
+      <c r="G128" s="52"/>
+      <c r="H128" s="52"/>
+      <c r="I128" s="52"/>
+      <c r="J128" s="52"/>
+      <c r="K128" s="52"/>
+      <c r="L128" s="52"/>
+      <c r="M128" s="52"/>
+      <c r="N128" s="52"/>
+      <c r="O128" s="52"/>
+      <c r="P128" s="52"/>
+      <c r="Q128" s="52"/>
+      <c r="R128" s="52"/>
+      <c r="S128" s="52"/>
+      <c r="T128" s="52"/>
+      <c r="U128" s="53"/>
     </row>
     <row r="129" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="65"/>
+      <c r="A129" s="62"/>
       <c r="B129" s="30" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C129" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D129" s="75"/>
-      <c r="E129" s="76"/>
-      <c r="F129" s="76"/>
-      <c r="G129" s="76"/>
-      <c r="H129" s="76"/>
-      <c r="I129" s="76"/>
-      <c r="J129" s="76"/>
-      <c r="K129" s="76"/>
-      <c r="L129" s="76"/>
-      <c r="M129" s="76"/>
-      <c r="N129" s="76"/>
-      <c r="O129" s="76"/>
-      <c r="P129" s="76"/>
-      <c r="Q129" s="76"/>
-      <c r="R129" s="76"/>
-      <c r="S129" s="76"/>
-      <c r="T129" s="76"/>
-      <c r="U129" s="77"/>
+      <c r="D129" s="51"/>
+      <c r="E129" s="52"/>
+      <c r="F129" s="52"/>
+      <c r="G129" s="52"/>
+      <c r="H129" s="52"/>
+      <c r="I129" s="52"/>
+      <c r="J129" s="52"/>
+      <c r="K129" s="52"/>
+      <c r="L129" s="52"/>
+      <c r="M129" s="52"/>
+      <c r="N129" s="52"/>
+      <c r="O129" s="52"/>
+      <c r="P129" s="52"/>
+      <c r="Q129" s="52"/>
+      <c r="R129" s="52"/>
+      <c r="S129" s="52"/>
+      <c r="T129" s="52"/>
+      <c r="U129" s="53"/>
     </row>
     <row r="130" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="60">
+      <c r="A130" s="57">
         <v>19</v>
       </c>
       <c r="B130" s="22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D130" s="75"/>
-      <c r="E130" s="76"/>
-      <c r="F130" s="76"/>
-      <c r="G130" s="76"/>
-      <c r="H130" s="76"/>
-      <c r="I130" s="76"/>
-      <c r="J130" s="76"/>
-      <c r="K130" s="76"/>
-      <c r="L130" s="76"/>
-      <c r="M130" s="76"/>
-      <c r="N130" s="76"/>
-      <c r="O130" s="76"/>
-      <c r="P130" s="76"/>
-      <c r="Q130" s="76"/>
-      <c r="R130" s="76"/>
-      <c r="S130" s="76"/>
-      <c r="T130" s="76"/>
-      <c r="U130" s="77"/>
+      <c r="D130" s="51"/>
+      <c r="E130" s="52"/>
+      <c r="F130" s="52"/>
+      <c r="G130" s="52"/>
+      <c r="H130" s="52"/>
+      <c r="I130" s="52"/>
+      <c r="J130" s="52"/>
+      <c r="K130" s="52"/>
+      <c r="L130" s="52"/>
+      <c r="M130" s="52"/>
+      <c r="N130" s="52"/>
+      <c r="O130" s="52"/>
+      <c r="P130" s="52"/>
+      <c r="Q130" s="52"/>
+      <c r="R130" s="52"/>
+      <c r="S130" s="52"/>
+      <c r="T130" s="52"/>
+      <c r="U130" s="53"/>
     </row>
     <row r="131" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="61"/>
+      <c r="A131" s="58"/>
       <c r="B131" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D131" s="75"/>
-      <c r="E131" s="76"/>
-      <c r="F131" s="76"/>
-      <c r="G131" s="76"/>
-      <c r="H131" s="76"/>
-      <c r="I131" s="76"/>
-      <c r="J131" s="76"/>
-      <c r="K131" s="76"/>
-      <c r="L131" s="76"/>
-      <c r="M131" s="76"/>
-      <c r="N131" s="76"/>
-      <c r="O131" s="76"/>
-      <c r="P131" s="76"/>
-      <c r="Q131" s="76"/>
-      <c r="R131" s="76"/>
-      <c r="S131" s="76"/>
-      <c r="T131" s="76"/>
-      <c r="U131" s="77"/>
+      <c r="D131" s="51"/>
+      <c r="E131" s="52"/>
+      <c r="F131" s="52"/>
+      <c r="G131" s="52"/>
+      <c r="H131" s="52"/>
+      <c r="I131" s="52"/>
+      <c r="J131" s="52"/>
+      <c r="K131" s="52"/>
+      <c r="L131" s="52"/>
+      <c r="M131" s="52"/>
+      <c r="N131" s="52"/>
+      <c r="O131" s="52"/>
+      <c r="P131" s="52"/>
+      <c r="Q131" s="52"/>
+      <c r="R131" s="52"/>
+      <c r="S131" s="52"/>
+      <c r="T131" s="52"/>
+      <c r="U131" s="53"/>
     </row>
     <row r="132" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="61"/>
+      <c r="A132" s="58"/>
       <c r="B132" s="22" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D132" s="75"/>
-      <c r="E132" s="76"/>
-      <c r="F132" s="76"/>
-      <c r="G132" s="76"/>
-      <c r="H132" s="76"/>
-      <c r="I132" s="76"/>
-      <c r="J132" s="76"/>
-      <c r="K132" s="76"/>
-      <c r="L132" s="76"/>
-      <c r="M132" s="76"/>
-      <c r="N132" s="76"/>
-      <c r="O132" s="76"/>
-      <c r="P132" s="76"/>
-      <c r="Q132" s="76"/>
-      <c r="R132" s="76"/>
-      <c r="S132" s="76"/>
-      <c r="T132" s="76"/>
-      <c r="U132" s="77"/>
+      <c r="D132" s="51"/>
+      <c r="E132" s="52"/>
+      <c r="F132" s="52"/>
+      <c r="G132" s="52"/>
+      <c r="H132" s="52"/>
+      <c r="I132" s="52"/>
+      <c r="J132" s="52"/>
+      <c r="K132" s="52"/>
+      <c r="L132" s="52"/>
+      <c r="M132" s="52"/>
+      <c r="N132" s="52"/>
+      <c r="O132" s="52"/>
+      <c r="P132" s="52"/>
+      <c r="Q132" s="52"/>
+      <c r="R132" s="52"/>
+      <c r="S132" s="52"/>
+      <c r="T132" s="52"/>
+      <c r="U132" s="53"/>
     </row>
     <row r="133" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="61"/>
+      <c r="A133" s="58"/>
       <c r="B133" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D133" s="75"/>
-      <c r="E133" s="76"/>
-      <c r="F133" s="76"/>
-      <c r="G133" s="76"/>
-      <c r="H133" s="76"/>
-      <c r="I133" s="76"/>
-      <c r="J133" s="76"/>
-      <c r="K133" s="76"/>
-      <c r="L133" s="76"/>
-      <c r="M133" s="76"/>
-      <c r="N133" s="76"/>
-      <c r="O133" s="76"/>
-      <c r="P133" s="76"/>
-      <c r="Q133" s="76"/>
-      <c r="R133" s="76"/>
-      <c r="S133" s="76"/>
-      <c r="T133" s="76"/>
-      <c r="U133" s="77"/>
+      <c r="D133" s="51"/>
+      <c r="E133" s="52"/>
+      <c r="F133" s="52"/>
+      <c r="G133" s="52"/>
+      <c r="H133" s="52"/>
+      <c r="I133" s="52"/>
+      <c r="J133" s="52"/>
+      <c r="K133" s="52"/>
+      <c r="L133" s="52"/>
+      <c r="M133" s="52"/>
+      <c r="N133" s="52"/>
+      <c r="O133" s="52"/>
+      <c r="P133" s="52"/>
+      <c r="Q133" s="52"/>
+      <c r="R133" s="52"/>
+      <c r="S133" s="52"/>
+      <c r="T133" s="52"/>
+      <c r="U133" s="53"/>
     </row>
     <row r="134" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="61"/>
+      <c r="A134" s="58"/>
       <c r="B134" s="22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D134" s="75"/>
-      <c r="E134" s="76"/>
-      <c r="F134" s="76"/>
-      <c r="G134" s="76"/>
-      <c r="H134" s="76"/>
-      <c r="I134" s="76"/>
-      <c r="J134" s="76"/>
-      <c r="K134" s="76"/>
-      <c r="L134" s="76"/>
-      <c r="M134" s="76"/>
-      <c r="N134" s="76"/>
-      <c r="O134" s="76"/>
-      <c r="P134" s="76"/>
-      <c r="Q134" s="76"/>
-      <c r="R134" s="76"/>
-      <c r="S134" s="76"/>
-      <c r="T134" s="76"/>
-      <c r="U134" s="77"/>
+      <c r="D134" s="51"/>
+      <c r="E134" s="52"/>
+      <c r="F134" s="52"/>
+      <c r="G134" s="52"/>
+      <c r="H134" s="52"/>
+      <c r="I134" s="52"/>
+      <c r="J134" s="52"/>
+      <c r="K134" s="52"/>
+      <c r="L134" s="52"/>
+      <c r="M134" s="52"/>
+      <c r="N134" s="52"/>
+      <c r="O134" s="52"/>
+      <c r="P134" s="52"/>
+      <c r="Q134" s="52"/>
+      <c r="R134" s="52"/>
+      <c r="S134" s="52"/>
+      <c r="T134" s="52"/>
+      <c r="U134" s="53"/>
     </row>
     <row r="135" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="61"/>
+      <c r="A135" s="58"/>
       <c r="B135" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D135" s="75"/>
-      <c r="E135" s="76"/>
-      <c r="F135" s="76"/>
-      <c r="G135" s="76"/>
-      <c r="H135" s="76"/>
-      <c r="I135" s="76"/>
-      <c r="J135" s="76"/>
-      <c r="K135" s="76"/>
-      <c r="L135" s="76"/>
-      <c r="M135" s="76"/>
-      <c r="N135" s="76"/>
-      <c r="O135" s="76"/>
-      <c r="P135" s="76"/>
-      <c r="Q135" s="76"/>
-      <c r="R135" s="76"/>
-      <c r="S135" s="76"/>
-      <c r="T135" s="76"/>
-      <c r="U135" s="77"/>
+      <c r="D135" s="51"/>
+      <c r="E135" s="52"/>
+      <c r="F135" s="52"/>
+      <c r="G135" s="52"/>
+      <c r="H135" s="52"/>
+      <c r="I135" s="52"/>
+      <c r="J135" s="52"/>
+      <c r="K135" s="52"/>
+      <c r="L135" s="52"/>
+      <c r="M135" s="52"/>
+      <c r="N135" s="52"/>
+      <c r="O135" s="52"/>
+      <c r="P135" s="52"/>
+      <c r="Q135" s="52"/>
+      <c r="R135" s="52"/>
+      <c r="S135" s="52"/>
+      <c r="T135" s="52"/>
+      <c r="U135" s="53"/>
     </row>
     <row r="136" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="62"/>
+      <c r="A136" s="59"/>
       <c r="B136" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D136" s="78"/>
-      <c r="E136" s="79"/>
-      <c r="F136" s="79"/>
-      <c r="G136" s="79"/>
-      <c r="H136" s="79"/>
-      <c r="I136" s="79"/>
-      <c r="J136" s="79"/>
-      <c r="K136" s="79"/>
-      <c r="L136" s="79"/>
-      <c r="M136" s="79"/>
-      <c r="N136" s="79"/>
-      <c r="O136" s="79"/>
-      <c r="P136" s="79"/>
-      <c r="Q136" s="79"/>
-      <c r="R136" s="79"/>
-      <c r="S136" s="79"/>
-      <c r="T136" s="79"/>
-      <c r="U136" s="80"/>
+      <c r="D136" s="54"/>
+      <c r="E136" s="55"/>
+      <c r="F136" s="55"/>
+      <c r="G136" s="55"/>
+      <c r="H136" s="55"/>
+      <c r="I136" s="55"/>
+      <c r="J136" s="55"/>
+      <c r="K136" s="55"/>
+      <c r="L136" s="55"/>
+      <c r="M136" s="55"/>
+      <c r="N136" s="55"/>
+      <c r="O136" s="55"/>
+      <c r="P136" s="55"/>
+      <c r="Q136" s="55"/>
+      <c r="R136" s="55"/>
+      <c r="S136" s="55"/>
+      <c r="T136" s="55"/>
+      <c r="U136" s="56"/>
     </row>
     <row r="137" spans="1:21"/>
     <row r="138" spans="1:21"/>
@@ -6795,26 +6798,6 @@
     <row r="150"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="D123:U136"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A81:A87"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="D29:U31"/>
@@ -6831,6 +6814,26 @@
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:C3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="D123:U136"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A123:A129"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6873,81 +6876,81 @@
   <sheetData>
     <row r="1" spans="1:27" ht="13.9" customHeight="1"/>
     <row r="2" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="77" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="81"/>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="48" t="s">
+      <c r="E2" s="64"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="49"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="48" t="s">
+      <c r="H2" s="64"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="49"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="48" t="s">
+      <c r="K2" s="64"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="49"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="48" t="s">
+      <c r="N2" s="64"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="48" t="s">
+      <c r="Q2" s="64"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="49"/>
-      <c r="U2" s="50"/>
+      <c r="T2" s="64"/>
+      <c r="U2" s="65"/>
     </row>
     <row r="3" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="67"/>
+      <c r="A3" s="76"/>
       <c r="B3" s="82"/>
       <c r="C3" s="83"/>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="49"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="48" t="s">
+      <c r="E3" s="64"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="49"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="48" t="s">
+      <c r="H3" s="64"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="49"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="48" t="s">
+      <c r="K3" s="64"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="49"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="48" t="s">
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="50"/>
-      <c r="S3" s="48" t="s">
+      <c r="Q3" s="64"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="49"/>
-      <c r="U3" s="50"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="65"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="60">
+      <c r="A4" s="57">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -7001,7 +7004,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="61"/>
+      <c r="A5" s="58"/>
       <c r="B5" s="6" t="s">
         <v>24</v>
       </c>
@@ -7061,7 +7064,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="61"/>
+      <c r="A6" s="58"/>
       <c r="B6" s="6" t="s">
         <v>28</v>
       </c>
@@ -7121,7 +7124,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="61"/>
+      <c r="A7" s="58"/>
       <c r="B7" s="6" t="s">
         <v>33</v>
       </c>
@@ -7179,7 +7182,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="61"/>
+      <c r="A8" s="58"/>
       <c r="B8" s="6" t="s">
         <v>37</v>
       </c>
@@ -7237,7 +7240,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="61"/>
+      <c r="A9" s="58"/>
       <c r="B9" s="6" t="s">
         <v>42</v>
       </c>
@@ -7287,7 +7290,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="62"/>
+      <c r="A10" s="59"/>
       <c r="B10" s="6" t="s">
         <v>46</v>
       </c>
@@ -7331,7 +7334,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="63">
+      <c r="A11" s="60">
         <v>2</v>
       </c>
       <c r="B11" s="14" t="s">
@@ -7393,7 +7396,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="64"/>
+      <c r="A12" s="61"/>
       <c r="B12" s="14" t="s">
         <v>51</v>
       </c>
@@ -7451,7 +7454,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="64"/>
+      <c r="A13" s="61"/>
       <c r="B13" s="14" t="s">
         <v>52</v>
       </c>
@@ -7521,7 +7524,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="64"/>
+      <c r="A14" s="61"/>
       <c r="B14" s="14" t="s">
         <v>56</v>
       </c>
@@ -7569,7 +7572,7 @@
       <c r="AA14" s="7"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="64"/>
+      <c r="A15" s="61"/>
       <c r="B15" s="14" t="s">
         <v>57</v>
       </c>
@@ -7610,7 +7613,7 @@
       <c r="U15" s="17"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="64"/>
+      <c r="A16" s="61"/>
       <c r="B16" s="14" t="s">
         <v>58</v>
       </c>
@@ -7645,7 +7648,7 @@
       <c r="U16" s="17"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="65"/>
+      <c r="A17" s="62"/>
       <c r="B17" s="14" t="s">
         <v>59</v>
       </c>
@@ -7672,7 +7675,7 @@
       <c r="U17" s="17"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="60">
+      <c r="A18" s="57">
         <v>3</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -7717,7 +7720,7 @@
       <c r="U18" s="9"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="61"/>
+      <c r="A19" s="58"/>
       <c r="B19" s="6" t="s">
         <v>61</v>
       </c>
@@ -7760,7 +7763,7 @@
       <c r="U19" s="9"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="61"/>
+      <c r="A20" s="58"/>
       <c r="B20" s="6" t="s">
         <v>62</v>
       </c>
@@ -7815,7 +7818,7 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="61"/>
+      <c r="A21" s="58"/>
       <c r="B21" s="6" t="s">
         <v>63</v>
       </c>
@@ -7858,7 +7861,7 @@
       <c r="U21" s="9"/>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="61"/>
+      <c r="A22" s="58"/>
       <c r="B22" s="6" t="s">
         <v>64</v>
       </c>
@@ -7899,7 +7902,7 @@
       <c r="U22" s="9"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="61"/>
+      <c r="A23" s="58"/>
       <c r="B23" s="6" t="s">
         <v>65</v>
       </c>
@@ -7926,7 +7929,7 @@
       <c r="U23" s="9"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="62"/>
+      <c r="A24" s="59"/>
       <c r="B24" s="23" t="s">
         <v>66</v>
       </c>
@@ -7965,7 +7968,7 @@
       <c r="U24" s="26"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="63">
+      <c r="A25" s="60">
         <v>4</v>
       </c>
       <c r="B25" s="14" t="s">
@@ -8010,7 +8013,7 @@
       <c r="U25" s="17"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="64"/>
+      <c r="A26" s="61"/>
       <c r="B26" s="14" t="s">
         <v>68</v>
       </c>
@@ -8053,7 +8056,7 @@
       <c r="U26" s="17"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="64"/>
+      <c r="A27" s="61"/>
       <c r="B27" s="14" t="s">
         <v>69</v>
       </c>
@@ -8108,7 +8111,7 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="64"/>
+      <c r="A28" s="61"/>
       <c r="B28" s="14" t="s">
         <v>70</v>
       </c>
@@ -8151,90 +8154,90 @@
       <c r="U28" s="17"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="64"/>
+      <c r="A29" s="61"/>
       <c r="B29" s="27" t="s">
         <v>71</v>
       </c>
       <c r="C29" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D29" s="51" t="s">
+      <c r="D29" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="E29" s="52"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="52"/>
-      <c r="J29" s="52"/>
-      <c r="K29" s="52"/>
-      <c r="L29" s="52"/>
-      <c r="M29" s="52"/>
-      <c r="N29" s="52"/>
-      <c r="O29" s="52"/>
-      <c r="P29" s="52"/>
-      <c r="Q29" s="52"/>
-      <c r="R29" s="52"/>
-      <c r="S29" s="52"/>
-      <c r="T29" s="52"/>
-      <c r="U29" s="53"/>
+      <c r="E29" s="67"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="67"/>
+      <c r="J29" s="67"/>
+      <c r="K29" s="67"/>
+      <c r="L29" s="67"/>
+      <c r="M29" s="67"/>
+      <c r="N29" s="67"/>
+      <c r="O29" s="67"/>
+      <c r="P29" s="67"/>
+      <c r="Q29" s="67"/>
+      <c r="R29" s="67"/>
+      <c r="S29" s="67"/>
+      <c r="T29" s="67"/>
+      <c r="U29" s="68"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="64"/>
+      <c r="A30" s="61"/>
       <c r="B30" s="27" t="s">
         <v>73</v>
       </c>
       <c r="C30" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="54"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="55"/>
-      <c r="J30" s="55"/>
-      <c r="K30" s="55"/>
-      <c r="L30" s="55"/>
-      <c r="M30" s="55"/>
-      <c r="N30" s="55"/>
-      <c r="O30" s="55"/>
-      <c r="P30" s="55"/>
-      <c r="Q30" s="55"/>
-      <c r="R30" s="55"/>
-      <c r="S30" s="55"/>
-      <c r="T30" s="55"/>
-      <c r="U30" s="56"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="70"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="70"/>
+      <c r="M30" s="70"/>
+      <c r="N30" s="70"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="70"/>
+      <c r="Q30" s="70"/>
+      <c r="R30" s="70"/>
+      <c r="S30" s="70"/>
+      <c r="T30" s="70"/>
+      <c r="U30" s="71"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="65"/>
+      <c r="A31" s="62"/>
       <c r="B31" s="27" t="s">
         <v>74</v>
       </c>
       <c r="C31" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D31" s="57"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="58"/>
-      <c r="N31" s="58"/>
-      <c r="O31" s="58"/>
-      <c r="P31" s="58"/>
-      <c r="Q31" s="58"/>
-      <c r="R31" s="58"/>
-      <c r="S31" s="58"/>
-      <c r="T31" s="58"/>
-      <c r="U31" s="59"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73"/>
+      <c r="J31" s="73"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="73"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="73"/>
+      <c r="O31" s="73"/>
+      <c r="P31" s="73"/>
+      <c r="Q31" s="73"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="73"/>
+      <c r="T31" s="73"/>
+      <c r="U31" s="74"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="60">
+      <c r="A32" s="57">
         <v>5</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -8250,7 +8253,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G32" s="6" t="s">
         <v>49</v>
@@ -8259,7 +8262,7 @@
         <v>50</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>19</v>
@@ -8279,7 +8282,7 @@
       <c r="U32" s="9"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="61"/>
+      <c r="A33" s="58"/>
       <c r="B33" s="6" t="s">
         <v>77</v>
       </c>
@@ -8303,7 +8306,7 @@
         <v>41</v>
       </c>
       <c r="L33" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>40</v>
@@ -8312,7 +8315,7 @@
         <v>41</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P33" s="6"/>
       <c r="Q33" s="8"/>
@@ -8322,9 +8325,9 @@
       <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="61"/>
+      <c r="A34" s="58"/>
       <c r="B34" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>29</v>
@@ -8365,202 +8368,202 @@
       <c r="U34" s="9"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="61"/>
+      <c r="A35" s="58"/>
       <c r="B35" s="29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="51" t="s">
+      <c r="D35" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="52"/>
-      <c r="N35" s="52"/>
-      <c r="O35" s="52"/>
-      <c r="P35" s="52"/>
-      <c r="Q35" s="52"/>
-      <c r="R35" s="52"/>
-      <c r="S35" s="52"/>
-      <c r="T35" s="52"/>
-      <c r="U35" s="53"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="67"/>
+      <c r="I35" s="67"/>
+      <c r="J35" s="67"/>
+      <c r="K35" s="67"/>
+      <c r="L35" s="67"/>
+      <c r="M35" s="67"/>
+      <c r="N35" s="67"/>
+      <c r="O35" s="67"/>
+      <c r="P35" s="67"/>
+      <c r="Q35" s="67"/>
+      <c r="R35" s="67"/>
+      <c r="S35" s="67"/>
+      <c r="T35" s="67"/>
+      <c r="U35" s="68"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="61"/>
+      <c r="A36" s="58"/>
       <c r="B36" s="29" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C36" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="54"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="55"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="55"/>
-      <c r="N36" s="55"/>
-      <c r="O36" s="55"/>
-      <c r="P36" s="55"/>
-      <c r="Q36" s="55"/>
-      <c r="R36" s="55"/>
-      <c r="S36" s="55"/>
-      <c r="T36" s="55"/>
-      <c r="U36" s="56"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="70"/>
+      <c r="K36" s="70"/>
+      <c r="L36" s="70"/>
+      <c r="M36" s="70"/>
+      <c r="N36" s="70"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="70"/>
+      <c r="Q36" s="70"/>
+      <c r="R36" s="70"/>
+      <c r="S36" s="70"/>
+      <c r="T36" s="70"/>
+      <c r="U36" s="71"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="61"/>
+      <c r="A37" s="58"/>
       <c r="B37" s="29" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C37" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="D37" s="54"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="55"/>
-      <c r="J37" s="55"/>
-      <c r="K37" s="55"/>
-      <c r="L37" s="55"/>
-      <c r="M37" s="55"/>
-      <c r="N37" s="55"/>
-      <c r="O37" s="55"/>
-      <c r="P37" s="55"/>
-      <c r="Q37" s="55"/>
-      <c r="R37" s="55"/>
-      <c r="S37" s="55"/>
-      <c r="T37" s="55"/>
-      <c r="U37" s="56"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="70"/>
+      <c r="H37" s="70"/>
+      <c r="I37" s="70"/>
+      <c r="J37" s="70"/>
+      <c r="K37" s="70"/>
+      <c r="L37" s="70"/>
+      <c r="M37" s="70"/>
+      <c r="N37" s="70"/>
+      <c r="O37" s="70"/>
+      <c r="P37" s="70"/>
+      <c r="Q37" s="70"/>
+      <c r="R37" s="70"/>
+      <c r="S37" s="70"/>
+      <c r="T37" s="70"/>
+      <c r="U37" s="71"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="62"/>
+      <c r="A38" s="59"/>
       <c r="B38" s="29" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C38" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D38" s="54"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="55"/>
-      <c r="J38" s="55"/>
-      <c r="K38" s="55"/>
-      <c r="L38" s="55"/>
-      <c r="M38" s="55"/>
-      <c r="N38" s="55"/>
-      <c r="O38" s="55"/>
-      <c r="P38" s="55"/>
-      <c r="Q38" s="55"/>
-      <c r="R38" s="55"/>
-      <c r="S38" s="55"/>
-      <c r="T38" s="55"/>
-      <c r="U38" s="56"/>
+      <c r="D38" s="69"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="70"/>
+      <c r="Q38" s="70"/>
+      <c r="R38" s="70"/>
+      <c r="S38" s="70"/>
+      <c r="T38" s="70"/>
+      <c r="U38" s="71"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="63">
+      <c r="A39" s="60">
         <v>6</v>
       </c>
       <c r="B39" s="29" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C39" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="54"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="55"/>
-      <c r="I39" s="55"/>
-      <c r="J39" s="55"/>
-      <c r="K39" s="55"/>
-      <c r="L39" s="55"/>
-      <c r="M39" s="55"/>
-      <c r="N39" s="55"/>
-      <c r="O39" s="55"/>
-      <c r="P39" s="55"/>
-      <c r="Q39" s="55"/>
-      <c r="R39" s="55"/>
-      <c r="S39" s="55"/>
-      <c r="T39" s="55"/>
-      <c r="U39" s="56"/>
+      <c r="D39" s="69"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="70"/>
+      <c r="M39" s="70"/>
+      <c r="N39" s="70"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="70"/>
+      <c r="Q39" s="70"/>
+      <c r="R39" s="70"/>
+      <c r="S39" s="70"/>
+      <c r="T39" s="70"/>
+      <c r="U39" s="71"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="64"/>
+      <c r="A40" s="61"/>
       <c r="B40" s="29" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C40" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="54"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="55"/>
-      <c r="J40" s="55"/>
-      <c r="K40" s="55"/>
-      <c r="L40" s="55"/>
-      <c r="M40" s="55"/>
-      <c r="N40" s="55"/>
-      <c r="O40" s="55"/>
-      <c r="P40" s="55"/>
-      <c r="Q40" s="55"/>
-      <c r="R40" s="55"/>
-      <c r="S40" s="55"/>
-      <c r="T40" s="55"/>
-      <c r="U40" s="56"/>
+      <c r="D40" s="69"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="70"/>
+      <c r="M40" s="70"/>
+      <c r="N40" s="70"/>
+      <c r="O40" s="70"/>
+      <c r="P40" s="70"/>
+      <c r="Q40" s="70"/>
+      <c r="R40" s="70"/>
+      <c r="S40" s="70"/>
+      <c r="T40" s="70"/>
+      <c r="U40" s="71"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="64"/>
+      <c r="A41" s="61"/>
       <c r="B41" s="29" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C41" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="D41" s="57"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="58"/>
-      <c r="N41" s="58"/>
-      <c r="O41" s="58"/>
-      <c r="P41" s="58"/>
-      <c r="Q41" s="58"/>
-      <c r="R41" s="58"/>
-      <c r="S41" s="58"/>
-      <c r="T41" s="58"/>
-      <c r="U41" s="59"/>
+      <c r="D41" s="72"/>
+      <c r="E41" s="73"/>
+      <c r="F41" s="73"/>
+      <c r="G41" s="73"/>
+      <c r="H41" s="73"/>
+      <c r="I41" s="73"/>
+      <c r="J41" s="73"/>
+      <c r="K41" s="73"/>
+      <c r="L41" s="73"/>
+      <c r="M41" s="73"/>
+      <c r="N41" s="73"/>
+      <c r="O41" s="73"/>
+      <c r="P41" s="73"/>
+      <c r="Q41" s="73"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="73"/>
+      <c r="T41" s="73"/>
+      <c r="U41" s="74"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="64"/>
+      <c r="A42" s="61"/>
       <c r="B42" s="30" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>34</v>
@@ -8582,7 +8585,7 @@
         <v>41</v>
       </c>
       <c r="L42" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M42" s="14" t="s">
         <v>40</v>
@@ -8591,7 +8594,7 @@
         <v>41</v>
       </c>
       <c r="O42" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P42" s="14"/>
       <c r="Q42" s="16"/>
@@ -8601,9 +8604,9 @@
       <c r="U42" s="17"/>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="64"/>
+      <c r="A43" s="61"/>
       <c r="B43" s="30" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>38</v>
@@ -8642,9 +8645,9 @@
       <c r="U43" s="17"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="64"/>
+      <c r="A44" s="61"/>
       <c r="B44" s="31" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C44" s="24" t="s">
         <v>43</v>
@@ -8669,9 +8672,9 @@
       <c r="U44" s="26"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="65"/>
+      <c r="A45" s="62"/>
       <c r="B45" s="30" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>47</v>
@@ -8696,11 +8699,11 @@
       <c r="U45" s="17"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="60">
+      <c r="A46" s="57">
         <v>7</v>
       </c>
       <c r="B46" s="22" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>15</v>
@@ -8712,7 +8715,7 @@
         <v>50</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G46" s="6" t="s">
         <v>49</v>
@@ -8721,7 +8724,7 @@
         <v>50</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>19</v>
@@ -8741,9 +8744,9 @@
       <c r="U46" s="9"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="61"/>
+      <c r="A47" s="58"/>
       <c r="B47" s="22" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>25</v>
@@ -8765,7 +8768,7 @@
         <v>41</v>
       </c>
       <c r="L47" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>40</v>
@@ -8774,7 +8777,7 @@
         <v>41</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P47" s="6"/>
       <c r="Q47" s="8"/>
@@ -8784,9 +8787,9 @@
       <c r="U47" s="9"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="61"/>
+      <c r="A48" s="58"/>
       <c r="B48" s="22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>29</v>
@@ -8827,9 +8830,9 @@
       <c r="U48" s="9"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="61"/>
+      <c r="A49" s="58"/>
       <c r="B49" s="22" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>34</v>
@@ -8851,7 +8854,7 @@
         <v>41</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>40</v>
@@ -8860,7 +8863,7 @@
         <v>41</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P49" s="6"/>
       <c r="Q49" s="8"/>
@@ -8870,9 +8873,9 @@
       <c r="U49" s="9"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="61"/>
+      <c r="A50" s="58"/>
       <c r="B50" s="22" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>38</v>
@@ -8911,9 +8914,9 @@
       <c r="U50" s="9"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="61"/>
+      <c r="A51" s="58"/>
       <c r="B51" s="22" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>43</v>
@@ -8946,9 +8949,9 @@
       <c r="U51" s="9"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="62"/>
+      <c r="A52" s="59"/>
       <c r="B52" s="22" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>47</v>
@@ -8973,11 +8976,11 @@
       <c r="U52" s="9"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="63">
+      <c r="A53" s="60">
         <v>8</v>
       </c>
       <c r="B53" s="30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C53" s="15" t="s">
         <v>15</v>
@@ -8989,7 +8992,7 @@
         <v>50</v>
       </c>
       <c r="F53" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G53" s="14" t="s">
         <v>49</v>
@@ -8998,7 +9001,7 @@
         <v>50</v>
       </c>
       <c r="I53" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J53" s="14" t="s">
         <v>19</v>
@@ -9018,9 +9021,9 @@
       <c r="U53" s="17"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="64"/>
+      <c r="A54" s="61"/>
       <c r="B54" s="30" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C54" s="15" t="s">
         <v>25</v>
@@ -9042,7 +9045,7 @@
         <v>41</v>
       </c>
       <c r="L54" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M54" s="14" t="s">
         <v>40</v>
@@ -9051,7 +9054,7 @@
         <v>41</v>
       </c>
       <c r="O54" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P54" s="14"/>
       <c r="Q54" s="16"/>
@@ -9061,9 +9064,9 @@
       <c r="U54" s="17"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="64"/>
+      <c r="A55" s="61"/>
       <c r="B55" s="30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C55" s="15" t="s">
         <v>29</v>
@@ -9116,9 +9119,9 @@
       </c>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="64"/>
+      <c r="A56" s="61"/>
       <c r="B56" s="30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C56" s="15" t="s">
         <v>34</v>
@@ -9140,7 +9143,7 @@
         <v>41</v>
       </c>
       <c r="L56" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M56" s="14" t="s">
         <v>40</v>
@@ -9149,7 +9152,7 @@
         <v>41</v>
       </c>
       <c r="O56" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P56" s="14"/>
       <c r="Q56" s="16"/>
@@ -9159,9 +9162,9 @@
       <c r="U56" s="17"/>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="64"/>
+      <c r="A57" s="61"/>
       <c r="B57" s="30" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C57" s="15" t="s">
         <v>38</v>
@@ -9200,9 +9203,9 @@
       <c r="U57" s="17"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="64"/>
+      <c r="A58" s="61"/>
       <c r="B58" s="30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>43</v>
@@ -9235,9 +9238,9 @@
       <c r="U58" s="17"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="65"/>
+      <c r="A59" s="62"/>
       <c r="B59" s="30" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>47</v>
@@ -9262,11 +9265,11 @@
       <c r="U59" s="17"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="60">
+      <c r="A60" s="57">
         <v>9</v>
       </c>
       <c r="B60" s="22" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>15</v>
@@ -9278,7 +9281,7 @@
         <v>50</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G60" s="6" t="s">
         <v>49</v>
@@ -9287,7 +9290,7 @@
         <v>50</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J60" s="6" t="s">
         <v>19</v>
@@ -9307,9 +9310,9 @@
       <c r="U60" s="9"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="61"/>
+      <c r="A61" s="58"/>
       <c r="B61" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>25</v>
@@ -9338,9 +9341,9 @@
       <c r="U61" s="9"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="61"/>
+      <c r="A62" s="58"/>
       <c r="B62" s="22" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>29</v>
@@ -9393,9 +9396,9 @@
       </c>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="61"/>
+      <c r="A63" s="58"/>
       <c r="B63" s="22" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>34</v>
@@ -9417,7 +9420,7 @@
         <v>41</v>
       </c>
       <c r="L63" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>40</v>
@@ -9426,7 +9429,7 @@
         <v>41</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P63" s="6"/>
       <c r="Q63" s="8"/>
@@ -9436,9 +9439,9 @@
       <c r="U63" s="32"/>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="61"/>
+      <c r="A64" s="58"/>
       <c r="B64" s="22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>38</v>
@@ -9479,9 +9482,9 @@
       <c r="U64" s="32"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="61"/>
+      <c r="A65" s="58"/>
       <c r="B65" s="22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>43</v>
@@ -9514,9 +9517,9 @@
       <c r="U65" s="32"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="62"/>
+      <c r="A66" s="59"/>
       <c r="B66" s="22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>47</v>
@@ -9541,11 +9544,11 @@
       <c r="U66" s="32"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="63">
+      <c r="A67" s="60">
         <v>10</v>
       </c>
       <c r="B67" s="30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>15</v>
@@ -9557,7 +9560,7 @@
         <v>50</v>
       </c>
       <c r="F67" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G67" s="14" t="s">
         <v>49</v>
@@ -9566,7 +9569,7 @@
         <v>50</v>
       </c>
       <c r="I67" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J67" s="14" t="s">
         <v>19</v>
@@ -9586,9 +9589,9 @@
       <c r="U67" s="33"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="64"/>
+      <c r="A68" s="61"/>
       <c r="B68" s="30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C68" s="15" t="s">
         <v>25</v>
@@ -9617,9 +9620,9 @@
       <c r="U68" s="33"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="64"/>
+      <c r="A69" s="61"/>
       <c r="B69" s="30" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C69" s="15" t="s">
         <v>29</v>
@@ -9660,9 +9663,9 @@
       <c r="U69" s="33"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="64"/>
+      <c r="A70" s="61"/>
       <c r="B70" s="30" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C70" s="15" t="s">
         <v>34</v>
@@ -9684,7 +9687,7 @@
         <v>41</v>
       </c>
       <c r="L70" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M70" s="14" t="s">
         <v>45</v>
@@ -9693,7 +9696,7 @@
         <v>41</v>
       </c>
       <c r="O70" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P70" s="14"/>
       <c r="Q70" s="16"/>
@@ -9703,9 +9706,9 @@
       <c r="U70" s="33"/>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="64"/>
+      <c r="A71" s="61"/>
       <c r="B71" s="30" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>38</v>
@@ -9746,9 +9749,9 @@
       <c r="U71" s="33"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="64"/>
+      <c r="A72" s="61"/>
       <c r="B72" s="30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>43</v>
@@ -9773,9 +9776,9 @@
       <c r="U72" s="33"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="65"/>
+      <c r="A73" s="62"/>
       <c r="B73" s="30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C73" s="15" t="s">
         <v>47</v>
@@ -9800,11 +9803,11 @@
       <c r="U73" s="33"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="60">
+      <c r="A74" s="57">
         <v>11</v>
       </c>
       <c r="B74" s="22" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>15</v>
@@ -9816,7 +9819,7 @@
         <v>50</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G74" s="6" t="s">
         <v>49</v>
@@ -9825,7 +9828,7 @@
         <v>50</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J74" s="6" t="s">
         <v>19</v>
@@ -9845,9 +9848,9 @@
       <c r="U74" s="32"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="61"/>
+      <c r="A75" s="58"/>
       <c r="B75" s="22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C75" s="7" t="s">
         <v>25</v>
@@ -9876,9 +9879,9 @@
       <c r="U75" s="32"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="61"/>
+      <c r="A76" s="58"/>
       <c r="B76" s="22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C76" s="7" t="s">
         <v>29</v>
@@ -9931,9 +9934,9 @@
       </c>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="61"/>
+      <c r="A77" s="58"/>
       <c r="B77" s="22" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C77" s="7" t="s">
         <v>34</v>
@@ -9955,7 +9958,7 @@
         <v>41</v>
       </c>
       <c r="L77" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>40</v>
@@ -9964,7 +9967,7 @@
         <v>41</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P77" s="6"/>
       <c r="Q77" s="8"/>
@@ -9974,9 +9977,9 @@
       <c r="U77" s="9"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="61"/>
+      <c r="A78" s="58"/>
       <c r="B78" s="22" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>38</v>
@@ -10017,9 +10020,9 @@
       <c r="U78" s="9"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="61"/>
+      <c r="A79" s="58"/>
       <c r="B79" s="22" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C79" s="7" t="s">
         <v>43</v>
@@ -10044,9 +10047,9 @@
       <c r="U79" s="9"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="62"/>
+      <c r="A80" s="59"/>
       <c r="B80" s="22" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C80" s="7" t="s">
         <v>47</v>
@@ -10071,11 +10074,11 @@
       <c r="U80" s="9"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="63">
+      <c r="A81" s="60">
         <v>12</v>
       </c>
       <c r="B81" s="30" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C81" s="15" t="s">
         <v>15</v>
@@ -10087,7 +10090,7 @@
         <v>50</v>
       </c>
       <c r="F81" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G81" s="14" t="s">
         <v>49</v>
@@ -10096,7 +10099,7 @@
         <v>50</v>
       </c>
       <c r="I81" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J81" s="14" t="s">
         <v>19</v>
@@ -10116,9 +10119,9 @@
       <c r="U81" s="17"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="64"/>
+      <c r="A82" s="61"/>
       <c r="B82" s="30" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>25</v>
@@ -10147,9 +10150,9 @@
       <c r="U82" s="17"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="64"/>
+      <c r="A83" s="61"/>
       <c r="B83" s="30" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>29</v>
@@ -10183,28 +10186,28 @@
       <c r="N83" s="16"/>
       <c r="O83" s="17"/>
       <c r="P83" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q83" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R83" s="17" t="s">
         <v>55</v>
       </c>
       <c r="S83" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T83" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U83" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="64"/>
+      <c r="A84" s="61"/>
       <c r="B84" s="30" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>34</v>
@@ -10226,7 +10229,7 @@
         <v>41</v>
       </c>
       <c r="L84" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M84" s="14" t="s">
         <v>45</v>
@@ -10235,7 +10238,7 @@
         <v>41</v>
       </c>
       <c r="O84" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P84" s="14"/>
       <c r="Q84" s="16"/>
@@ -10245,9 +10248,9 @@
       <c r="U84" s="17"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="64"/>
+      <c r="A85" s="61"/>
       <c r="B85" s="30" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C85" s="15" t="s">
         <v>38</v>
@@ -10288,9 +10291,9 @@
       <c r="U85" s="17"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="64"/>
+      <c r="A86" s="61"/>
       <c r="B86" s="30" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C86" s="15" t="s">
         <v>43</v>
@@ -10323,9 +10326,9 @@
       <c r="U86" s="17"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="65"/>
+      <c r="A87" s="62"/>
       <c r="B87" s="30" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>47</v>
@@ -10350,11 +10353,11 @@
       <c r="U87" s="17"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="60">
+      <c r="A88" s="57">
         <v>13</v>
       </c>
       <c r="B88" s="22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>15</v>
@@ -10366,7 +10369,7 @@
         <v>50</v>
       </c>
       <c r="F88" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G88" s="6" t="s">
         <v>49</v>
@@ -10375,7 +10378,7 @@
         <v>50</v>
       </c>
       <c r="I88" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J88" s="6" t="s">
         <v>19</v>
@@ -10395,9 +10398,9 @@
       <c r="U88" s="9"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="61"/>
+      <c r="A89" s="58"/>
       <c r="B89" s="22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C89" s="7" t="s">
         <v>25</v>
@@ -10426,9 +10429,9 @@
       <c r="U89" s="9"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="61"/>
+      <c r="A90" s="58"/>
       <c r="B90" s="22" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C90" s="7" t="s">
         <v>29</v>
@@ -10462,28 +10465,28 @@
       <c r="N90" s="8"/>
       <c r="O90" s="9"/>
       <c r="P90" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q90" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R90" s="9" t="s">
         <v>55</v>
       </c>
       <c r="S90" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T90" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U90" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="61"/>
+      <c r="A91" s="58"/>
       <c r="B91" s="22" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C91" s="7" t="s">
         <v>34</v>
@@ -10505,7 +10508,7 @@
         <v>41</v>
       </c>
       <c r="L91" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M91" s="6" t="s">
         <v>40</v>
@@ -10514,7 +10517,7 @@
         <v>41</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P91" s="6"/>
       <c r="Q91" s="8"/>
@@ -10524,9 +10527,9 @@
       <c r="U91" s="9"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="61"/>
+      <c r="A92" s="58"/>
       <c r="B92" s="22" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C92" s="7" t="s">
         <v>38</v>
@@ -10567,9 +10570,9 @@
       <c r="U92" s="9"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="61"/>
+      <c r="A93" s="58"/>
       <c r="B93" s="22" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C93" s="7" t="s">
         <v>43</v>
@@ -10602,9 +10605,9 @@
       <c r="U93" s="9"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="62"/>
+      <c r="A94" s="59"/>
       <c r="B94" s="22" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C94" s="7" t="s">
         <v>47</v>
@@ -10629,11 +10632,11 @@
       <c r="U94" s="9"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="63">
+      <c r="A95" s="60">
         <v>14</v>
       </c>
       <c r="B95" s="30" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C95" s="15" t="s">
         <v>15</v>
@@ -10645,7 +10648,7 @@
         <v>50</v>
       </c>
       <c r="F95" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G95" s="14" t="s">
         <v>49</v>
@@ -10654,7 +10657,7 @@
         <v>50</v>
       </c>
       <c r="I95" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J95" s="14" t="s">
         <v>19</v>
@@ -10674,9 +10677,9 @@
       <c r="U95" s="17"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="64"/>
+      <c r="A96" s="61"/>
       <c r="B96" s="30" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C96" s="15" t="s">
         <v>25</v>
@@ -10705,9 +10708,9 @@
       <c r="U96" s="17"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="64"/>
+      <c r="A97" s="61"/>
       <c r="B97" s="30" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C97" s="15" t="s">
         <v>29</v>
@@ -10741,28 +10744,28 @@
       <c r="N97" s="16"/>
       <c r="O97" s="17"/>
       <c r="P97" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q97" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R97" s="17" t="s">
         <v>55</v>
       </c>
       <c r="S97" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T97" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U97" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="64"/>
+      <c r="A98" s="61"/>
       <c r="B98" s="30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C98" s="15" t="s">
         <v>34</v>
@@ -10784,7 +10787,7 @@
         <v>41</v>
       </c>
       <c r="L98" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M98" s="14" t="s">
         <v>45</v>
@@ -10793,7 +10796,7 @@
         <v>41</v>
       </c>
       <c r="O98" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P98" s="14"/>
       <c r="Q98" s="16"/>
@@ -10803,9 +10806,9 @@
       <c r="U98" s="17"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="64"/>
+      <c r="A99" s="61"/>
       <c r="B99" s="30" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C99" s="15" t="s">
         <v>38</v>
@@ -10846,9 +10849,9 @@
       <c r="U99" s="17"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="64"/>
+      <c r="A100" s="61"/>
       <c r="B100" s="30" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C100" s="15" t="s">
         <v>43</v>
@@ -10873,9 +10876,9 @@
       <c r="U100" s="17"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="65"/>
+      <c r="A101" s="62"/>
       <c r="B101" s="30" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C101" s="15" t="s">
         <v>47</v>
@@ -10900,11 +10903,11 @@
       <c r="U101" s="17"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="60">
+      <c r="A102" s="57">
         <v>15</v>
       </c>
       <c r="B102" s="22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C102" s="7" t="s">
         <v>15</v>
@@ -10916,7 +10919,7 @@
         <v>50</v>
       </c>
       <c r="F102" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G102" s="6" t="s">
         <v>49</v>
@@ -10925,7 +10928,7 @@
         <v>50</v>
       </c>
       <c r="I102" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J102" s="6" t="s">
         <v>19</v>
@@ -10945,9 +10948,9 @@
       <c r="U102" s="9"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="61"/>
+      <c r="A103" s="58"/>
       <c r="B103" s="22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>25</v>
@@ -10976,9 +10979,9 @@
       <c r="U103" s="9"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="61"/>
+      <c r="A104" s="58"/>
       <c r="B104" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C104" s="7" t="s">
         <v>29</v>
@@ -11012,28 +11015,28 @@
       <c r="N104" s="8"/>
       <c r="O104" s="9"/>
       <c r="P104" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q104" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R104" s="9" t="s">
         <v>55</v>
       </c>
       <c r="S104" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T104" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U104" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="61"/>
+      <c r="A105" s="58"/>
       <c r="B105" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>34</v>
@@ -11055,7 +11058,7 @@
         <v>41</v>
       </c>
       <c r="L105" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M105" s="6" t="s">
         <v>40</v>
@@ -11064,7 +11067,7 @@
         <v>41</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P105" s="6"/>
       <c r="Q105" s="8"/>
@@ -11074,9 +11077,9 @@
       <c r="U105" s="9"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="61"/>
+      <c r="A106" s="58"/>
       <c r="B106" s="22" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C106" s="7" t="s">
         <v>38</v>
@@ -11117,9 +11120,9 @@
       <c r="U106" s="9"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="61"/>
+      <c r="A107" s="58"/>
       <c r="B107" s="22" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C107" s="7" t="s">
         <v>43</v>
@@ -11152,9 +11155,9 @@
       <c r="U107" s="9"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="62"/>
+      <c r="A108" s="59"/>
       <c r="B108" s="22" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C108" s="7" t="s">
         <v>47</v>
@@ -11179,11 +11182,11 @@
       <c r="U108" s="9"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="63">
+      <c r="A109" s="60">
         <v>16</v>
       </c>
       <c r="B109" s="30" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C109" s="15" t="s">
         <v>15</v>
@@ -11195,7 +11198,7 @@
         <v>50</v>
       </c>
       <c r="F109" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G109" s="14" t="s">
         <v>49</v>
@@ -11204,7 +11207,7 @@
         <v>50</v>
       </c>
       <c r="I109" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J109" s="14" t="s">
         <v>19</v>
@@ -11224,9 +11227,9 @@
       <c r="U109" s="33"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="64"/>
+      <c r="A110" s="61"/>
       <c r="B110" s="30" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C110" s="15" t="s">
         <v>25</v>
@@ -11255,9 +11258,9 @@
       <c r="U110" s="33"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="64"/>
+      <c r="A111" s="61"/>
       <c r="B111" s="30" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C111" s="15" t="s">
         <v>29</v>
@@ -11291,28 +11294,28 @@
       <c r="N111" s="16"/>
       <c r="O111" s="17"/>
       <c r="P111" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q111" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R111" s="17" t="s">
         <v>55</v>
       </c>
       <c r="S111" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T111" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U111" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="64"/>
+      <c r="A112" s="61"/>
       <c r="B112" s="30" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C112" s="15" t="s">
         <v>34</v>
@@ -11334,7 +11337,7 @@
         <v>41</v>
       </c>
       <c r="L112" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M112" s="14" t="s">
         <v>45</v>
@@ -11343,7 +11346,7 @@
         <v>41</v>
       </c>
       <c r="O112" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P112" s="14"/>
       <c r="Q112" s="16"/>
@@ -11353,9 +11356,9 @@
       <c r="U112" s="33"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="64"/>
+      <c r="A113" s="61"/>
       <c r="B113" s="30" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C113" s="15" t="s">
         <v>38</v>
@@ -11396,9 +11399,9 @@
       <c r="U113" s="33"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="64"/>
+      <c r="A114" s="61"/>
       <c r="B114" s="30" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C114" s="15" t="s">
         <v>43</v>
@@ -11423,9 +11426,9 @@
       <c r="U114" s="33"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="65"/>
+      <c r="A115" s="62"/>
       <c r="B115" s="30" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C115" s="15" t="s">
         <v>47</v>
@@ -11450,11 +11453,11 @@
       <c r="U115" s="33"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="60">
+      <c r="A116" s="57">
         <v>17</v>
       </c>
       <c r="B116" s="22" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C116" s="7" t="s">
         <v>15</v>
@@ -11466,7 +11469,7 @@
         <v>50</v>
       </c>
       <c r="F116" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G116" s="6" t="s">
         <v>49</v>
@@ -11475,7 +11478,7 @@
         <v>50</v>
       </c>
       <c r="I116" s="9" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J116" s="6"/>
       <c r="K116" s="8"/>
@@ -11493,9 +11496,9 @@
       <c r="U116" s="9"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="61"/>
+      <c r="A117" s="58"/>
       <c r="B117" s="22" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>25</v>
@@ -11522,9 +11525,9 @@
       <c r="U117" s="9"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="61"/>
+      <c r="A118" s="58"/>
       <c r="B118" s="22" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C118" s="7" t="s">
         <v>29</v>
@@ -11544,28 +11547,28 @@
       <c r="N118" s="8"/>
       <c r="O118" s="9"/>
       <c r="P118" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q118" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R118" s="9" t="s">
         <v>55</v>
       </c>
       <c r="S118" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T118" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U118" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="61"/>
+      <c r="A119" s="58"/>
       <c r="B119" s="22" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>34</v>
@@ -11585,7 +11588,7 @@
         <v>41</v>
       </c>
       <c r="L119" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M119" s="6" t="s">
         <v>40</v>
@@ -11594,7 +11597,7 @@
         <v>41</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="P119" s="6"/>
       <c r="Q119" s="8"/>
@@ -11604,9 +11607,9 @@
       <c r="U119" s="9"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="61"/>
+      <c r="A120" s="58"/>
       <c r="B120" s="22" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C120" s="7" t="s">
         <v>38</v>
@@ -11647,9 +11650,9 @@
       <c r="U120" s="9"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="61"/>
+      <c r="A121" s="58"/>
       <c r="B121" s="22" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>43</v>
@@ -11674,9 +11677,9 @@
       <c r="U121" s="9"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="62"/>
+      <c r="A122" s="59"/>
       <c r="B122" s="22" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>47</v>
@@ -11701,388 +11704,388 @@
       <c r="U122" s="9"/>
     </row>
     <row r="123" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="60">
+      <c r="A123" s="57">
         <v>18</v>
       </c>
       <c r="B123" s="22" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C123" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D123" s="72" t="s">
-        <v>171</v>
-      </c>
-      <c r="E123" s="73"/>
-      <c r="F123" s="73"/>
-      <c r="G123" s="73"/>
-      <c r="H123" s="73"/>
-      <c r="I123" s="73"/>
-      <c r="J123" s="73"/>
-      <c r="K123" s="73"/>
-      <c r="L123" s="73"/>
-      <c r="M123" s="73"/>
-      <c r="N123" s="73"/>
-      <c r="O123" s="73"/>
-      <c r="P123" s="73"/>
-      <c r="Q123" s="73"/>
-      <c r="R123" s="73"/>
-      <c r="S123" s="73"/>
-      <c r="T123" s="73"/>
-      <c r="U123" s="74"/>
+      <c r="D123" s="48" t="s">
+        <v>172</v>
+      </c>
+      <c r="E123" s="49"/>
+      <c r="F123" s="49"/>
+      <c r="G123" s="49"/>
+      <c r="H123" s="49"/>
+      <c r="I123" s="49"/>
+      <c r="J123" s="49"/>
+      <c r="K123" s="49"/>
+      <c r="L123" s="49"/>
+      <c r="M123" s="49"/>
+      <c r="N123" s="49"/>
+      <c r="O123" s="49"/>
+      <c r="P123" s="49"/>
+      <c r="Q123" s="49"/>
+      <c r="R123" s="49"/>
+      <c r="S123" s="49"/>
+      <c r="T123" s="49"/>
+      <c r="U123" s="50"/>
     </row>
     <row r="124" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="61"/>
+      <c r="A124" s="58"/>
       <c r="B124" s="22" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C124" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D124" s="75"/>
-      <c r="E124" s="76"/>
-      <c r="F124" s="76"/>
-      <c r="G124" s="76"/>
-      <c r="H124" s="76"/>
-      <c r="I124" s="76"/>
-      <c r="J124" s="76"/>
-      <c r="K124" s="76"/>
-      <c r="L124" s="76"/>
-      <c r="M124" s="76"/>
-      <c r="N124" s="76"/>
-      <c r="O124" s="76"/>
-      <c r="P124" s="76"/>
-      <c r="Q124" s="76"/>
-      <c r="R124" s="76"/>
-      <c r="S124" s="76"/>
-      <c r="T124" s="76"/>
-      <c r="U124" s="77"/>
+      <c r="D124" s="51"/>
+      <c r="E124" s="52"/>
+      <c r="F124" s="52"/>
+      <c r="G124" s="52"/>
+      <c r="H124" s="52"/>
+      <c r="I124" s="52"/>
+      <c r="J124" s="52"/>
+      <c r="K124" s="52"/>
+      <c r="L124" s="52"/>
+      <c r="M124" s="52"/>
+      <c r="N124" s="52"/>
+      <c r="O124" s="52"/>
+      <c r="P124" s="52"/>
+      <c r="Q124" s="52"/>
+      <c r="R124" s="52"/>
+      <c r="S124" s="52"/>
+      <c r="T124" s="52"/>
+      <c r="U124" s="53"/>
     </row>
     <row r="125" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="61"/>
+      <c r="A125" s="58"/>
       <c r="B125" s="22" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C125" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D125" s="75"/>
-      <c r="E125" s="76"/>
-      <c r="F125" s="76"/>
-      <c r="G125" s="76"/>
-      <c r="H125" s="76"/>
-      <c r="I125" s="76"/>
-      <c r="J125" s="76"/>
-      <c r="K125" s="76"/>
-      <c r="L125" s="76"/>
-      <c r="M125" s="76"/>
-      <c r="N125" s="76"/>
-      <c r="O125" s="76"/>
-      <c r="P125" s="76"/>
-      <c r="Q125" s="76"/>
-      <c r="R125" s="76"/>
-      <c r="S125" s="76"/>
-      <c r="T125" s="76"/>
-      <c r="U125" s="77"/>
+      <c r="D125" s="51"/>
+      <c r="E125" s="52"/>
+      <c r="F125" s="52"/>
+      <c r="G125" s="52"/>
+      <c r="H125" s="52"/>
+      <c r="I125" s="52"/>
+      <c r="J125" s="52"/>
+      <c r="K125" s="52"/>
+      <c r="L125" s="52"/>
+      <c r="M125" s="52"/>
+      <c r="N125" s="52"/>
+      <c r="O125" s="52"/>
+      <c r="P125" s="52"/>
+      <c r="Q125" s="52"/>
+      <c r="R125" s="52"/>
+      <c r="S125" s="52"/>
+      <c r="T125" s="52"/>
+      <c r="U125" s="53"/>
     </row>
     <row r="126" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="61"/>
+      <c r="A126" s="58"/>
       <c r="B126" s="22" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C126" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D126" s="75"/>
-      <c r="E126" s="76"/>
-      <c r="F126" s="76"/>
-      <c r="G126" s="76"/>
-      <c r="H126" s="76"/>
-      <c r="I126" s="76"/>
-      <c r="J126" s="76"/>
-      <c r="K126" s="76"/>
-      <c r="L126" s="76"/>
-      <c r="M126" s="76"/>
-      <c r="N126" s="76"/>
-      <c r="O126" s="76"/>
-      <c r="P126" s="76"/>
-      <c r="Q126" s="76"/>
-      <c r="R126" s="76"/>
-      <c r="S126" s="76"/>
-      <c r="T126" s="76"/>
-      <c r="U126" s="77"/>
+      <c r="D126" s="51"/>
+      <c r="E126" s="52"/>
+      <c r="F126" s="52"/>
+      <c r="G126" s="52"/>
+      <c r="H126" s="52"/>
+      <c r="I126" s="52"/>
+      <c r="J126" s="52"/>
+      <c r="K126" s="52"/>
+      <c r="L126" s="52"/>
+      <c r="M126" s="52"/>
+      <c r="N126" s="52"/>
+      <c r="O126" s="52"/>
+      <c r="P126" s="52"/>
+      <c r="Q126" s="52"/>
+      <c r="R126" s="52"/>
+      <c r="S126" s="52"/>
+      <c r="T126" s="52"/>
+      <c r="U126" s="53"/>
     </row>
     <row r="127" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="61"/>
+      <c r="A127" s="58"/>
       <c r="B127" s="29" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C127" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D127" s="75"/>
-      <c r="E127" s="76"/>
-      <c r="F127" s="76"/>
-      <c r="G127" s="76"/>
-      <c r="H127" s="76"/>
-      <c r="I127" s="76"/>
-      <c r="J127" s="76"/>
-      <c r="K127" s="76"/>
-      <c r="L127" s="76"/>
-      <c r="M127" s="76"/>
-      <c r="N127" s="76"/>
-      <c r="O127" s="76"/>
-      <c r="P127" s="76"/>
-      <c r="Q127" s="76"/>
-      <c r="R127" s="76"/>
-      <c r="S127" s="76"/>
-      <c r="T127" s="76"/>
-      <c r="U127" s="77"/>
+      <c r="D127" s="51"/>
+      <c r="E127" s="52"/>
+      <c r="F127" s="52"/>
+      <c r="G127" s="52"/>
+      <c r="H127" s="52"/>
+      <c r="I127" s="52"/>
+      <c r="J127" s="52"/>
+      <c r="K127" s="52"/>
+      <c r="L127" s="52"/>
+      <c r="M127" s="52"/>
+      <c r="N127" s="52"/>
+      <c r="O127" s="52"/>
+      <c r="P127" s="52"/>
+      <c r="Q127" s="52"/>
+      <c r="R127" s="52"/>
+      <c r="S127" s="52"/>
+      <c r="T127" s="52"/>
+      <c r="U127" s="53"/>
     </row>
     <row r="128" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="61"/>
+      <c r="A128" s="58"/>
       <c r="B128" s="22" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C128" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D128" s="75"/>
-      <c r="E128" s="76"/>
-      <c r="F128" s="76"/>
-      <c r="G128" s="76"/>
-      <c r="H128" s="76"/>
-      <c r="I128" s="76"/>
-      <c r="J128" s="76"/>
-      <c r="K128" s="76"/>
-      <c r="L128" s="76"/>
-      <c r="M128" s="76"/>
-      <c r="N128" s="76"/>
-      <c r="O128" s="76"/>
-      <c r="P128" s="76"/>
-      <c r="Q128" s="76"/>
-      <c r="R128" s="76"/>
-      <c r="S128" s="76"/>
-      <c r="T128" s="76"/>
-      <c r="U128" s="77"/>
+      <c r="D128" s="51"/>
+      <c r="E128" s="52"/>
+      <c r="F128" s="52"/>
+      <c r="G128" s="52"/>
+      <c r="H128" s="52"/>
+      <c r="I128" s="52"/>
+      <c r="J128" s="52"/>
+      <c r="K128" s="52"/>
+      <c r="L128" s="52"/>
+      <c r="M128" s="52"/>
+      <c r="N128" s="52"/>
+      <c r="O128" s="52"/>
+      <c r="P128" s="52"/>
+      <c r="Q128" s="52"/>
+      <c r="R128" s="52"/>
+      <c r="S128" s="52"/>
+      <c r="T128" s="52"/>
+      <c r="U128" s="53"/>
     </row>
     <row r="129" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="62"/>
+      <c r="A129" s="59"/>
       <c r="B129" s="22" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C129" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D129" s="75"/>
-      <c r="E129" s="76"/>
-      <c r="F129" s="76"/>
-      <c r="G129" s="76"/>
-      <c r="H129" s="76"/>
-      <c r="I129" s="76"/>
-      <c r="J129" s="76"/>
-      <c r="K129" s="76"/>
-      <c r="L129" s="76"/>
-      <c r="M129" s="76"/>
-      <c r="N129" s="76"/>
-      <c r="O129" s="76"/>
-      <c r="P129" s="76"/>
-      <c r="Q129" s="76"/>
-      <c r="R129" s="76"/>
-      <c r="S129" s="76"/>
-      <c r="T129" s="76"/>
-      <c r="U129" s="77"/>
+      <c r="D129" s="51"/>
+      <c r="E129" s="52"/>
+      <c r="F129" s="52"/>
+      <c r="G129" s="52"/>
+      <c r="H129" s="52"/>
+      <c r="I129" s="52"/>
+      <c r="J129" s="52"/>
+      <c r="K129" s="52"/>
+      <c r="L129" s="52"/>
+      <c r="M129" s="52"/>
+      <c r="N129" s="52"/>
+      <c r="O129" s="52"/>
+      <c r="P129" s="52"/>
+      <c r="Q129" s="52"/>
+      <c r="R129" s="52"/>
+      <c r="S129" s="52"/>
+      <c r="T129" s="52"/>
+      <c r="U129" s="53"/>
     </row>
     <row r="130" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="60">
+      <c r="A130" s="57">
         <v>19</v>
       </c>
       <c r="B130" s="22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D130" s="75"/>
-      <c r="E130" s="76"/>
-      <c r="F130" s="76"/>
-      <c r="G130" s="76"/>
-      <c r="H130" s="76"/>
-      <c r="I130" s="76"/>
-      <c r="J130" s="76"/>
-      <c r="K130" s="76"/>
-      <c r="L130" s="76"/>
-      <c r="M130" s="76"/>
-      <c r="N130" s="76"/>
-      <c r="O130" s="76"/>
-      <c r="P130" s="76"/>
-      <c r="Q130" s="76"/>
-      <c r="R130" s="76"/>
-      <c r="S130" s="76"/>
-      <c r="T130" s="76"/>
-      <c r="U130" s="77"/>
+      <c r="D130" s="51"/>
+      <c r="E130" s="52"/>
+      <c r="F130" s="52"/>
+      <c r="G130" s="52"/>
+      <c r="H130" s="52"/>
+      <c r="I130" s="52"/>
+      <c r="J130" s="52"/>
+      <c r="K130" s="52"/>
+      <c r="L130" s="52"/>
+      <c r="M130" s="52"/>
+      <c r="N130" s="52"/>
+      <c r="O130" s="52"/>
+      <c r="P130" s="52"/>
+      <c r="Q130" s="52"/>
+      <c r="R130" s="52"/>
+      <c r="S130" s="52"/>
+      <c r="T130" s="52"/>
+      <c r="U130" s="53"/>
     </row>
     <row r="131" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="61"/>
+      <c r="A131" s="58"/>
       <c r="B131" s="22" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D131" s="75"/>
-      <c r="E131" s="76"/>
-      <c r="F131" s="76"/>
-      <c r="G131" s="76"/>
-      <c r="H131" s="76"/>
-      <c r="I131" s="76"/>
-      <c r="J131" s="76"/>
-      <c r="K131" s="76"/>
-      <c r="L131" s="76"/>
-      <c r="M131" s="76"/>
-      <c r="N131" s="76"/>
-      <c r="O131" s="76"/>
-      <c r="P131" s="76"/>
-      <c r="Q131" s="76"/>
-      <c r="R131" s="76"/>
-      <c r="S131" s="76"/>
-      <c r="T131" s="76"/>
-      <c r="U131" s="77"/>
+      <c r="D131" s="51"/>
+      <c r="E131" s="52"/>
+      <c r="F131" s="52"/>
+      <c r="G131" s="52"/>
+      <c r="H131" s="52"/>
+      <c r="I131" s="52"/>
+      <c r="J131" s="52"/>
+      <c r="K131" s="52"/>
+      <c r="L131" s="52"/>
+      <c r="M131" s="52"/>
+      <c r="N131" s="52"/>
+      <c r="O131" s="52"/>
+      <c r="P131" s="52"/>
+      <c r="Q131" s="52"/>
+      <c r="R131" s="52"/>
+      <c r="S131" s="52"/>
+      <c r="T131" s="52"/>
+      <c r="U131" s="53"/>
     </row>
     <row r="132" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="61"/>
+      <c r="A132" s="58"/>
       <c r="B132" s="22" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D132" s="75"/>
-      <c r="E132" s="76"/>
-      <c r="F132" s="76"/>
-      <c r="G132" s="76"/>
-      <c r="H132" s="76"/>
-      <c r="I132" s="76"/>
-      <c r="J132" s="76"/>
-      <c r="K132" s="76"/>
-      <c r="L132" s="76"/>
-      <c r="M132" s="76"/>
-      <c r="N132" s="76"/>
-      <c r="O132" s="76"/>
-      <c r="P132" s="76"/>
-      <c r="Q132" s="76"/>
-      <c r="R132" s="76"/>
-      <c r="S132" s="76"/>
-      <c r="T132" s="76"/>
-      <c r="U132" s="77"/>
+      <c r="D132" s="51"/>
+      <c r="E132" s="52"/>
+      <c r="F132" s="52"/>
+      <c r="G132" s="52"/>
+      <c r="H132" s="52"/>
+      <c r="I132" s="52"/>
+      <c r="J132" s="52"/>
+      <c r="K132" s="52"/>
+      <c r="L132" s="52"/>
+      <c r="M132" s="52"/>
+      <c r="N132" s="52"/>
+      <c r="O132" s="52"/>
+      <c r="P132" s="52"/>
+      <c r="Q132" s="52"/>
+      <c r="R132" s="52"/>
+      <c r="S132" s="52"/>
+      <c r="T132" s="52"/>
+      <c r="U132" s="53"/>
     </row>
     <row r="133" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="61"/>
+      <c r="A133" s="58"/>
       <c r="B133" s="22" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D133" s="75"/>
-      <c r="E133" s="76"/>
-      <c r="F133" s="76"/>
-      <c r="G133" s="76"/>
-      <c r="H133" s="76"/>
-      <c r="I133" s="76"/>
-      <c r="J133" s="76"/>
-      <c r="K133" s="76"/>
-      <c r="L133" s="76"/>
-      <c r="M133" s="76"/>
-      <c r="N133" s="76"/>
-      <c r="O133" s="76"/>
-      <c r="P133" s="76"/>
-      <c r="Q133" s="76"/>
-      <c r="R133" s="76"/>
-      <c r="S133" s="76"/>
-      <c r="T133" s="76"/>
-      <c r="U133" s="77"/>
+      <c r="D133" s="51"/>
+      <c r="E133" s="52"/>
+      <c r="F133" s="52"/>
+      <c r="G133" s="52"/>
+      <c r="H133" s="52"/>
+      <c r="I133" s="52"/>
+      <c r="J133" s="52"/>
+      <c r="K133" s="52"/>
+      <c r="L133" s="52"/>
+      <c r="M133" s="52"/>
+      <c r="N133" s="52"/>
+      <c r="O133" s="52"/>
+      <c r="P133" s="52"/>
+      <c r="Q133" s="52"/>
+      <c r="R133" s="52"/>
+      <c r="S133" s="52"/>
+      <c r="T133" s="52"/>
+      <c r="U133" s="53"/>
     </row>
     <row r="134" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="61"/>
+      <c r="A134" s="58"/>
       <c r="B134" s="22" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D134" s="75"/>
-      <c r="E134" s="76"/>
-      <c r="F134" s="76"/>
-      <c r="G134" s="76"/>
-      <c r="H134" s="76"/>
-      <c r="I134" s="76"/>
-      <c r="J134" s="76"/>
-      <c r="K134" s="76"/>
-      <c r="L134" s="76"/>
-      <c r="M134" s="76"/>
-      <c r="N134" s="76"/>
-      <c r="O134" s="76"/>
-      <c r="P134" s="76"/>
-      <c r="Q134" s="76"/>
-      <c r="R134" s="76"/>
-      <c r="S134" s="76"/>
-      <c r="T134" s="76"/>
-      <c r="U134" s="77"/>
+      <c r="D134" s="51"/>
+      <c r="E134" s="52"/>
+      <c r="F134" s="52"/>
+      <c r="G134" s="52"/>
+      <c r="H134" s="52"/>
+      <c r="I134" s="52"/>
+      <c r="J134" s="52"/>
+      <c r="K134" s="52"/>
+      <c r="L134" s="52"/>
+      <c r="M134" s="52"/>
+      <c r="N134" s="52"/>
+      <c r="O134" s="52"/>
+      <c r="P134" s="52"/>
+      <c r="Q134" s="52"/>
+      <c r="R134" s="52"/>
+      <c r="S134" s="52"/>
+      <c r="T134" s="52"/>
+      <c r="U134" s="53"/>
     </row>
     <row r="135" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="61"/>
+      <c r="A135" s="58"/>
       <c r="B135" s="22" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D135" s="75"/>
-      <c r="E135" s="76"/>
-      <c r="F135" s="76"/>
-      <c r="G135" s="76"/>
-      <c r="H135" s="76"/>
-      <c r="I135" s="76"/>
-      <c r="J135" s="76"/>
-      <c r="K135" s="76"/>
-      <c r="L135" s="76"/>
-      <c r="M135" s="76"/>
-      <c r="N135" s="76"/>
-      <c r="O135" s="76"/>
-      <c r="P135" s="76"/>
-      <c r="Q135" s="76"/>
-      <c r="R135" s="76"/>
-      <c r="S135" s="76"/>
-      <c r="T135" s="76"/>
-      <c r="U135" s="77"/>
+      <c r="D135" s="51"/>
+      <c r="E135" s="52"/>
+      <c r="F135" s="52"/>
+      <c r="G135" s="52"/>
+      <c r="H135" s="52"/>
+      <c r="I135" s="52"/>
+      <c r="J135" s="52"/>
+      <c r="K135" s="52"/>
+      <c r="L135" s="52"/>
+      <c r="M135" s="52"/>
+      <c r="N135" s="52"/>
+      <c r="O135" s="52"/>
+      <c r="P135" s="52"/>
+      <c r="Q135" s="52"/>
+      <c r="R135" s="52"/>
+      <c r="S135" s="52"/>
+      <c r="T135" s="52"/>
+      <c r="U135" s="53"/>
     </row>
     <row r="136" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="62"/>
+      <c r="A136" s="59"/>
       <c r="B136" s="22" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D136" s="78"/>
-      <c r="E136" s="79"/>
-      <c r="F136" s="79"/>
-      <c r="G136" s="79"/>
-      <c r="H136" s="79"/>
-      <c r="I136" s="79"/>
-      <c r="J136" s="79"/>
-      <c r="K136" s="79"/>
-      <c r="L136" s="79"/>
-      <c r="M136" s="79"/>
-      <c r="N136" s="79"/>
-      <c r="O136" s="79"/>
-      <c r="P136" s="79"/>
-      <c r="Q136" s="79"/>
-      <c r="R136" s="79"/>
-      <c r="S136" s="79"/>
-      <c r="T136" s="79"/>
-      <c r="U136" s="80"/>
+      <c r="D136" s="54"/>
+      <c r="E136" s="55"/>
+      <c r="F136" s="55"/>
+      <c r="G136" s="55"/>
+      <c r="H136" s="55"/>
+      <c r="I136" s="55"/>
+      <c r="J136" s="55"/>
+      <c r="K136" s="55"/>
+      <c r="L136" s="55"/>
+      <c r="M136" s="55"/>
+      <c r="N136" s="55"/>
+      <c r="O136" s="55"/>
+      <c r="P136" s="55"/>
+      <c r="Q136" s="55"/>
+      <c r="R136" s="55"/>
+      <c r="S136" s="55"/>
+      <c r="T136" s="55"/>
+      <c r="U136" s="56"/>
     </row>
     <row r="137" spans="1:21"/>
     <row r="138" spans="1:21"/>
@@ -12100,26 +12103,6 @@
     <row r="150"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="D123:U136"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A81:A87"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="D29:U31"/>
@@ -12136,6 +12119,26 @@
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:C3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="D123:U136"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A123:A129"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12178,81 +12181,81 @@
   <sheetData>
     <row r="1" spans="1:27" ht="13.9" customHeight="1"/>
     <row r="2" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="48" t="s">
+      <c r="C2" s="78"/>
+      <c r="D2" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="49"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="48" t="s">
+      <c r="E2" s="64"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="63" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="49"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="48" t="s">
+      <c r="H2" s="64"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="49"/>
-      <c r="L2" s="50"/>
-      <c r="M2" s="48" t="s">
+      <c r="K2" s="64"/>
+      <c r="L2" s="65"/>
+      <c r="M2" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="49"/>
-      <c r="O2" s="50"/>
-      <c r="P2" s="48" t="s">
+      <c r="N2" s="64"/>
+      <c r="O2" s="65"/>
+      <c r="P2" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="50"/>
-      <c r="S2" s="48" t="s">
+      <c r="Q2" s="64"/>
+      <c r="R2" s="65"/>
+      <c r="S2" s="63" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="49"/>
-      <c r="U2" s="50"/>
+      <c r="T2" s="64"/>
+      <c r="U2" s="65"/>
     </row>
     <row r="3" spans="1:27" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="67"/>
-      <c r="B3" s="70"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="48" t="s">
+      <c r="A3" s="76"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="49"/>
-      <c r="F3" s="50"/>
-      <c r="G3" s="48" t="s">
+      <c r="E3" s="64"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="49"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="48" t="s">
+      <c r="H3" s="64"/>
+      <c r="I3" s="65"/>
+      <c r="J3" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="49"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="48" t="s">
+      <c r="K3" s="64"/>
+      <c r="L3" s="65"/>
+      <c r="M3" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="49"/>
-      <c r="O3" s="50"/>
-      <c r="P3" s="48" t="s">
+      <c r="N3" s="64"/>
+      <c r="O3" s="65"/>
+      <c r="P3" s="63" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="49"/>
-      <c r="R3" s="50"/>
-      <c r="S3" s="48" t="s">
+      <c r="Q3" s="64"/>
+      <c r="R3" s="65"/>
+      <c r="S3" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="49"/>
-      <c r="U3" s="50"/>
+      <c r="T3" s="64"/>
+      <c r="U3" s="65"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="60">
+      <c r="A4" s="57">
         <v>1</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -12306,7 +12309,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="61"/>
+      <c r="A5" s="58"/>
       <c r="B5" s="6" t="s">
         <v>24</v>
       </c>
@@ -12351,7 +12354,7 @@
         <v>26</v>
       </c>
       <c r="X5" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="Y5" s="11">
         <v>64</v>
@@ -12366,7 +12369,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="61"/>
+      <c r="A6" s="58"/>
       <c r="B6" s="6" t="s">
         <v>28</v>
       </c>
@@ -12377,19 +12380,19 @@
         <v>26</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>26</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J6" s="6" t="s">
         <v>19</v>
@@ -12426,7 +12429,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="61"/>
+      <c r="A7" s="58"/>
       <c r="B7" s="6" t="s">
         <v>33</v>
       </c>
@@ -12484,7 +12487,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="61"/>
+      <c r="A8" s="58"/>
       <c r="B8" s="6" t="s">
         <v>37</v>
       </c>
@@ -12542,7 +12545,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="61"/>
+      <c r="A9" s="58"/>
       <c r="B9" s="6" t="s">
         <v>42</v>
       </c>
@@ -12592,7 +12595,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="62"/>
+      <c r="A10" s="59"/>
       <c r="B10" s="6" t="s">
         <v>46</v>
       </c>
@@ -12636,7 +12639,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="63">
+      <c r="A11" s="60">
         <v>2</v>
       </c>
       <c r="B11" s="14" t="s">
@@ -12698,7 +12701,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="64"/>
+      <c r="A12" s="61"/>
       <c r="B12" s="14" t="s">
         <v>51</v>
       </c>
@@ -12756,7 +12759,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="64"/>
+      <c r="A13" s="61"/>
       <c r="B13" s="14" t="s">
         <v>52</v>
       </c>
@@ -12767,19 +12770,19 @@
         <v>26</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>26</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I13" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J13" s="14" t="s">
         <v>19</v>
@@ -12826,7 +12829,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="64"/>
+      <c r="A14" s="61"/>
       <c r="B14" s="14" t="s">
         <v>56</v>
       </c>
@@ -12874,7 +12877,7 @@
       <c r="AA14" s="7"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="64"/>
+      <c r="A15" s="61"/>
       <c r="B15" s="14" t="s">
         <v>57</v>
       </c>
@@ -12915,7 +12918,7 @@
       <c r="U15" s="17"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="64"/>
+      <c r="A16" s="61"/>
       <c r="B16" s="14" t="s">
         <v>58</v>
       </c>
@@ -12950,7 +12953,7 @@
       <c r="U16" s="17"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="65"/>
+      <c r="A17" s="62"/>
       <c r="B17" s="14" t="s">
         <v>59</v>
       </c>
@@ -12977,7 +12980,7 @@
       <c r="U17" s="17"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="60">
+      <c r="A18" s="57">
         <v>3</v>
       </c>
       <c r="B18" s="6" t="s">
@@ -13022,7 +13025,7 @@
       <c r="U18" s="9"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="61"/>
+      <c r="A19" s="58"/>
       <c r="B19" s="6" t="s">
         <v>61</v>
       </c>
@@ -13065,7 +13068,7 @@
       <c r="U19" s="9"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="61"/>
+      <c r="A20" s="58"/>
       <c r="B20" s="6" t="s">
         <v>62</v>
       </c>
@@ -13076,19 +13079,19 @@
         <v>26</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G20" s="6" t="s">
         <v>26</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>19</v>
@@ -13120,7 +13123,7 @@
       </c>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="61"/>
+      <c r="A21" s="58"/>
       <c r="B21" s="6" t="s">
         <v>63</v>
       </c>
@@ -13163,7 +13166,7 @@
       <c r="U21" s="9"/>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="61"/>
+      <c r="A22" s="58"/>
       <c r="B22" s="6" t="s">
         <v>64</v>
       </c>
@@ -13204,7 +13207,7 @@
       <c r="U22" s="9"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="61"/>
+      <c r="A23" s="58"/>
       <c r="B23" s="6" t="s">
         <v>65</v>
       </c>
@@ -13231,7 +13234,7 @@
       <c r="U23" s="9"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="62"/>
+      <c r="A24" s="59"/>
       <c r="B24" s="23" t="s">
         <v>66</v>
       </c>
@@ -13270,7 +13273,7 @@
       <c r="U24" s="26"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="63">
+      <c r="A25" s="60">
         <v>4</v>
       </c>
       <c r="B25" s="14" t="s">
@@ -13315,7 +13318,7 @@
       <c r="U25" s="17"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="64"/>
+      <c r="A26" s="61"/>
       <c r="B26" s="14" t="s">
         <v>68</v>
       </c>
@@ -13358,7 +13361,7 @@
       <c r="U26" s="17"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="64"/>
+      <c r="A27" s="61"/>
       <c r="B27" s="14" t="s">
         <v>69</v>
       </c>
@@ -13369,19 +13372,19 @@
         <v>26</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F27" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G27" s="14" t="s">
         <v>26</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J27" s="14" t="s">
         <v>19</v>
@@ -13413,7 +13416,7 @@
       </c>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="64"/>
+      <c r="A28" s="61"/>
       <c r="B28" s="14" t="s">
         <v>70</v>
       </c>
@@ -13456,90 +13459,90 @@
       <c r="U28" s="17"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="64"/>
+      <c r="A29" s="61"/>
       <c r="B29" s="27" t="s">
         <v>71</v>
       </c>
       <c r="C29" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D29" s="51" t="s">
+      <c r="D29" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="E29" s="52"/>
-      <c r="F29" s="52"/>
-      <c r="G29" s="52"/>
-      <c r="H29" s="52"/>
-      <c r="I29" s="52"/>
-      <c r="J29" s="52"/>
-      <c r="K29" s="52"/>
-      <c r="L29" s="52"/>
-      <c r="M29" s="52"/>
-      <c r="N29" s="52"/>
-      <c r="O29" s="52"/>
-      <c r="P29" s="52"/>
-      <c r="Q29" s="52"/>
-      <c r="R29" s="52"/>
-      <c r="S29" s="52"/>
-      <c r="T29" s="52"/>
-      <c r="U29" s="53"/>
+      <c r="E29" s="67"/>
+      <c r="F29" s="67"/>
+      <c r="G29" s="67"/>
+      <c r="H29" s="67"/>
+      <c r="I29" s="67"/>
+      <c r="J29" s="67"/>
+      <c r="K29" s="67"/>
+      <c r="L29" s="67"/>
+      <c r="M29" s="67"/>
+      <c r="N29" s="67"/>
+      <c r="O29" s="67"/>
+      <c r="P29" s="67"/>
+      <c r="Q29" s="67"/>
+      <c r="R29" s="67"/>
+      <c r="S29" s="67"/>
+      <c r="T29" s="67"/>
+      <c r="U29" s="68"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="64"/>
+      <c r="A30" s="61"/>
       <c r="B30" s="27" t="s">
         <v>73</v>
       </c>
       <c r="C30" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="D30" s="54"/>
-      <c r="E30" s="55"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="55"/>
-      <c r="I30" s="55"/>
-      <c r="J30" s="55"/>
-      <c r="K30" s="55"/>
-      <c r="L30" s="55"/>
-      <c r="M30" s="55"/>
-      <c r="N30" s="55"/>
-      <c r="O30" s="55"/>
-      <c r="P30" s="55"/>
-      <c r="Q30" s="55"/>
-      <c r="R30" s="55"/>
-      <c r="S30" s="55"/>
-      <c r="T30" s="55"/>
-      <c r="U30" s="56"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="70"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="70"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="70"/>
+      <c r="M30" s="70"/>
+      <c r="N30" s="70"/>
+      <c r="O30" s="70"/>
+      <c r="P30" s="70"/>
+      <c r="Q30" s="70"/>
+      <c r="R30" s="70"/>
+      <c r="S30" s="70"/>
+      <c r="T30" s="70"/>
+      <c r="U30" s="71"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="65"/>
+      <c r="A31" s="62"/>
       <c r="B31" s="27" t="s">
         <v>74</v>
       </c>
       <c r="C31" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D31" s="57"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="58"/>
-      <c r="K31" s="58"/>
-      <c r="L31" s="58"/>
-      <c r="M31" s="58"/>
-      <c r="N31" s="58"/>
-      <c r="O31" s="58"/>
-      <c r="P31" s="58"/>
-      <c r="Q31" s="58"/>
-      <c r="R31" s="58"/>
-      <c r="S31" s="58"/>
-      <c r="T31" s="58"/>
-      <c r="U31" s="59"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73"/>
+      <c r="J31" s="73"/>
+      <c r="K31" s="73"/>
+      <c r="L31" s="73"/>
+      <c r="M31" s="73"/>
+      <c r="N31" s="73"/>
+      <c r="O31" s="73"/>
+      <c r="P31" s="73"/>
+      <c r="Q31" s="73"/>
+      <c r="R31" s="73"/>
+      <c r="S31" s="73"/>
+      <c r="T31" s="73"/>
+      <c r="U31" s="74"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="60">
+      <c r="A32" s="57">
         <v>5</v>
       </c>
       <c r="B32" s="6" t="s">
@@ -13584,7 +13587,7 @@
       <c r="U32" s="9"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="61"/>
+      <c r="A33" s="58"/>
       <c r="B33" s="6" t="s">
         <v>77</v>
       </c>
@@ -13615,9 +13618,9 @@
       <c r="U33" s="9"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="61"/>
+      <c r="A34" s="58"/>
       <c r="B34" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>29</v>
@@ -13626,19 +13629,19 @@
         <v>26</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>19</v>
@@ -13658,202 +13661,202 @@
       <c r="U34" s="9"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="61"/>
+      <c r="A35" s="58"/>
       <c r="B35" s="34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="D35" s="51" t="s">
+      <c r="D35" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="52"/>
-      <c r="N35" s="52"/>
-      <c r="O35" s="52"/>
-      <c r="P35" s="52"/>
-      <c r="Q35" s="52"/>
-      <c r="R35" s="52"/>
-      <c r="S35" s="52"/>
-      <c r="T35" s="52"/>
-      <c r="U35" s="53"/>
+      <c r="E35" s="67"/>
+      <c r="F35" s="67"/>
+      <c r="G35" s="67"/>
+      <c r="H35" s="67"/>
+      <c r="I35" s="67"/>
+      <c r="J35" s="67"/>
+      <c r="K35" s="67"/>
+      <c r="L35" s="67"/>
+      <c r="M35" s="67"/>
+      <c r="N35" s="67"/>
+      <c r="O35" s="67"/>
+      <c r="P35" s="67"/>
+      <c r="Q35" s="67"/>
+      <c r="R35" s="67"/>
+      <c r="S35" s="67"/>
+      <c r="T35" s="67"/>
+      <c r="U35" s="68"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="61"/>
+      <c r="A36" s="58"/>
       <c r="B36" s="34" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C36" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D36" s="54"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="55"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="55"/>
-      <c r="N36" s="55"/>
-      <c r="O36" s="55"/>
-      <c r="P36" s="55"/>
-      <c r="Q36" s="55"/>
-      <c r="R36" s="55"/>
-      <c r="S36" s="55"/>
-      <c r="T36" s="55"/>
-      <c r="U36" s="56"/>
+      <c r="D36" s="69"/>
+      <c r="E36" s="70"/>
+      <c r="F36" s="70"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="70"/>
+      <c r="I36" s="70"/>
+      <c r="J36" s="70"/>
+      <c r="K36" s="70"/>
+      <c r="L36" s="70"/>
+      <c r="M36" s="70"/>
+      <c r="N36" s="70"/>
+      <c r="O36" s="70"/>
+      <c r="P36" s="70"/>
+      <c r="Q36" s="70"/>
+      <c r="R36" s="70"/>
+      <c r="S36" s="70"/>
+      <c r="T36" s="70"/>
+      <c r="U36" s="71"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="61"/>
+      <c r="A37" s="58"/>
       <c r="B37" s="34" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C37" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="D37" s="54"/>
-      <c r="E37" s="55"/>
-      <c r="F37" s="55"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="55"/>
-      <c r="J37" s="55"/>
-      <c r="K37" s="55"/>
-      <c r="L37" s="55"/>
-      <c r="M37" s="55"/>
-      <c r="N37" s="55"/>
-      <c r="O37" s="55"/>
-      <c r="P37" s="55"/>
-      <c r="Q37" s="55"/>
-      <c r="R37" s="55"/>
-      <c r="S37" s="55"/>
-      <c r="T37" s="55"/>
-      <c r="U37" s="56"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="70"/>
+      <c r="F37" s="70"/>
+      <c r="G37" s="70"/>
+      <c r="H37" s="70"/>
+      <c r="I37" s="70"/>
+      <c r="J37" s="70"/>
+      <c r="K37" s="70"/>
+      <c r="L37" s="70"/>
+      <c r="M37" s="70"/>
+      <c r="N37" s="70"/>
+      <c r="O37" s="70"/>
+      <c r="P37" s="70"/>
+      <c r="Q37" s="70"/>
+      <c r="R37" s="70"/>
+      <c r="S37" s="70"/>
+      <c r="T37" s="70"/>
+      <c r="U37" s="71"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="62"/>
+      <c r="A38" s="59"/>
       <c r="B38" s="34" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C38" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="D38" s="54"/>
-      <c r="E38" s="55"/>
-      <c r="F38" s="55"/>
-      <c r="G38" s="55"/>
-      <c r="H38" s="55"/>
-      <c r="I38" s="55"/>
-      <c r="J38" s="55"/>
-      <c r="K38" s="55"/>
-      <c r="L38" s="55"/>
-      <c r="M38" s="55"/>
-      <c r="N38" s="55"/>
-      <c r="O38" s="55"/>
-      <c r="P38" s="55"/>
-      <c r="Q38" s="55"/>
-      <c r="R38" s="55"/>
-      <c r="S38" s="55"/>
-      <c r="T38" s="55"/>
-      <c r="U38" s="56"/>
+      <c r="D38" s="69"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="70"/>
+      <c r="Q38" s="70"/>
+      <c r="R38" s="70"/>
+      <c r="S38" s="70"/>
+      <c r="T38" s="70"/>
+      <c r="U38" s="71"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="63">
+      <c r="A39" s="60">
         <v>6</v>
       </c>
       <c r="B39" s="34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C39" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="54"/>
-      <c r="E39" s="55"/>
-      <c r="F39" s="55"/>
-      <c r="G39" s="55"/>
-      <c r="H39" s="55"/>
-      <c r="I39" s="55"/>
-      <c r="J39" s="55"/>
-      <c r="K39" s="55"/>
-      <c r="L39" s="55"/>
-      <c r="M39" s="55"/>
-      <c r="N39" s="55"/>
-      <c r="O39" s="55"/>
-      <c r="P39" s="55"/>
-      <c r="Q39" s="55"/>
-      <c r="R39" s="55"/>
-      <c r="S39" s="55"/>
-      <c r="T39" s="55"/>
-      <c r="U39" s="56"/>
+      <c r="D39" s="69"/>
+      <c r="E39" s="70"/>
+      <c r="F39" s="70"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="70"/>
+      <c r="I39" s="70"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="70"/>
+      <c r="L39" s="70"/>
+      <c r="M39" s="70"/>
+      <c r="N39" s="70"/>
+      <c r="O39" s="70"/>
+      <c r="P39" s="70"/>
+      <c r="Q39" s="70"/>
+      <c r="R39" s="70"/>
+      <c r="S39" s="70"/>
+      <c r="T39" s="70"/>
+      <c r="U39" s="71"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="64"/>
+      <c r="A40" s="61"/>
       <c r="B40" s="34" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C40" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="D40" s="54"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
-      <c r="H40" s="55"/>
-      <c r="I40" s="55"/>
-      <c r="J40" s="55"/>
-      <c r="K40" s="55"/>
-      <c r="L40" s="55"/>
-      <c r="M40" s="55"/>
-      <c r="N40" s="55"/>
-      <c r="O40" s="55"/>
-      <c r="P40" s="55"/>
-      <c r="Q40" s="55"/>
-      <c r="R40" s="55"/>
-      <c r="S40" s="55"/>
-      <c r="T40" s="55"/>
-      <c r="U40" s="56"/>
+      <c r="D40" s="69"/>
+      <c r="E40" s="70"/>
+      <c r="F40" s="70"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="70"/>
+      <c r="I40" s="70"/>
+      <c r="J40" s="70"/>
+      <c r="K40" s="70"/>
+      <c r="L40" s="70"/>
+      <c r="M40" s="70"/>
+      <c r="N40" s="70"/>
+      <c r="O40" s="70"/>
+      <c r="P40" s="70"/>
+      <c r="Q40" s="70"/>
+      <c r="R40" s="70"/>
+      <c r="S40" s="70"/>
+      <c r="T40" s="70"/>
+      <c r="U40" s="71"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="64"/>
+      <c r="A41" s="61"/>
       <c r="B41" s="34" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C41" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="D41" s="57"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
-      <c r="J41" s="58"/>
-      <c r="K41" s="58"/>
-      <c r="L41" s="58"/>
-      <c r="M41" s="58"/>
-      <c r="N41" s="58"/>
-      <c r="O41" s="58"/>
-      <c r="P41" s="58"/>
-      <c r="Q41" s="58"/>
-      <c r="R41" s="58"/>
-      <c r="S41" s="58"/>
-      <c r="T41" s="58"/>
-      <c r="U41" s="59"/>
+      <c r="D41" s="72"/>
+      <c r="E41" s="73"/>
+      <c r="F41" s="73"/>
+      <c r="G41" s="73"/>
+      <c r="H41" s="73"/>
+      <c r="I41" s="73"/>
+      <c r="J41" s="73"/>
+      <c r="K41" s="73"/>
+      <c r="L41" s="73"/>
+      <c r="M41" s="73"/>
+      <c r="N41" s="73"/>
+      <c r="O41" s="73"/>
+      <c r="P41" s="73"/>
+      <c r="Q41" s="73"/>
+      <c r="R41" s="73"/>
+      <c r="S41" s="73"/>
+      <c r="T41" s="73"/>
+      <c r="U41" s="74"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="64"/>
+      <c r="A42" s="61"/>
       <c r="B42" s="35" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C42" s="15" t="s">
         <v>34</v>
@@ -13875,7 +13878,7 @@
         <v>50</v>
       </c>
       <c r="L42" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M42" s="14" t="s">
         <v>49</v>
@@ -13884,7 +13887,7 @@
         <v>50</v>
       </c>
       <c r="O42" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P42" s="14"/>
       <c r="Q42" s="16"/>
@@ -13894,9 +13897,9 @@
       <c r="U42" s="17"/>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="64"/>
+      <c r="A43" s="61"/>
       <c r="B43" s="35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C43" s="15" t="s">
         <v>38</v>
@@ -13908,7 +13911,7 @@
         <v>41</v>
       </c>
       <c r="F43" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G43" s="14" t="s">
         <v>40</v>
@@ -13917,7 +13920,7 @@
         <v>41</v>
       </c>
       <c r="I43" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J43" s="14"/>
       <c r="K43" s="16"/>
@@ -13935,9 +13938,9 @@
       <c r="U43" s="17"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="64"/>
+      <c r="A44" s="61"/>
       <c r="B44" s="36" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C44" s="24" t="s">
         <v>43</v>
@@ -13962,9 +13965,9 @@
       <c r="U44" s="26"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="65"/>
+      <c r="A45" s="62"/>
       <c r="B45" s="35" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C45" s="15" t="s">
         <v>47</v>
@@ -13989,11 +13992,11 @@
       <c r="U45" s="17"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="60">
+      <c r="A46" s="57">
         <v>7</v>
       </c>
       <c r="B46" s="37" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C46" s="7" t="s">
         <v>15</v>
@@ -14034,9 +14037,9 @@
       <c r="U46" s="9"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="61"/>
+      <c r="A47" s="58"/>
       <c r="B47" s="37" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C47" s="7" t="s">
         <v>25</v>
@@ -14065,9 +14068,9 @@
       <c r="U47" s="9"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="61"/>
+      <c r="A48" s="58"/>
       <c r="B48" s="37" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C48" s="7" t="s">
         <v>29</v>
@@ -14076,19 +14079,19 @@
         <v>26</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J48" s="6" t="s">
         <v>19</v>
@@ -14108,9 +14111,9 @@
       <c r="U48" s="9"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="61"/>
+      <c r="A49" s="58"/>
       <c r="B49" s="37" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C49" s="7" t="s">
         <v>34</v>
@@ -14132,7 +14135,7 @@
         <v>50</v>
       </c>
       <c r="L49" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>49</v>
@@ -14141,7 +14144,7 @@
         <v>50</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P49" s="6"/>
       <c r="Q49" s="8"/>
@@ -14151,9 +14154,9 @@
       <c r="U49" s="9"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="61"/>
+      <c r="A50" s="58"/>
       <c r="B50" s="37" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C50" s="7" t="s">
         <v>38</v>
@@ -14165,7 +14168,7 @@
         <v>41</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G50" s="6" t="s">
         <v>40</v>
@@ -14174,7 +14177,7 @@
         <v>41</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J50" s="6"/>
       <c r="K50" s="8"/>
@@ -14192,9 +14195,9 @@
       <c r="U50" s="9"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="61"/>
+      <c r="A51" s="58"/>
       <c r="B51" s="37" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C51" s="7" t="s">
         <v>43</v>
@@ -14227,9 +14230,9 @@
       <c r="U51" s="9"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="62"/>
+      <c r="A52" s="59"/>
       <c r="B52" s="37" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C52" s="7" t="s">
         <v>47</v>
@@ -14254,11 +14257,11 @@
       <c r="U52" s="9"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="63">
+      <c r="A53" s="60">
         <v>8</v>
       </c>
       <c r="B53" s="35" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C53" s="15" t="s">
         <v>15</v>
@@ -14299,9 +14302,9 @@
       <c r="U53" s="17"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="64"/>
+      <c r="A54" s="61"/>
       <c r="B54" s="35" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C54" s="15" t="s">
         <v>25</v>
@@ -14330,9 +14333,9 @@
       <c r="U54" s="17"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="64"/>
+      <c r="A55" s="61"/>
       <c r="B55" s="35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C55" s="15" t="s">
         <v>29</v>
@@ -14341,19 +14344,19 @@
         <v>26</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F55" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G55" s="14" t="s">
         <v>26</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I55" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J55" s="14" t="s">
         <v>19</v>
@@ -14385,9 +14388,9 @@
       </c>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="64"/>
+      <c r="A56" s="61"/>
       <c r="B56" s="35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C56" s="15" t="s">
         <v>34</v>
@@ -14409,7 +14412,7 @@
         <v>50</v>
       </c>
       <c r="L56" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M56" s="14" t="s">
         <v>49</v>
@@ -14418,7 +14421,7 @@
         <v>50</v>
       </c>
       <c r="O56" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P56" s="14"/>
       <c r="Q56" s="16"/>
@@ -14428,9 +14431,9 @@
       <c r="U56" s="17"/>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="64"/>
+      <c r="A57" s="61"/>
       <c r="B57" s="35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C57" s="15" t="s">
         <v>38</v>
@@ -14442,7 +14445,7 @@
         <v>41</v>
       </c>
       <c r="F57" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G57" s="14" t="s">
         <v>40</v>
@@ -14451,7 +14454,7 @@
         <v>41</v>
       </c>
       <c r="I57" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J57" s="14" t="s">
         <v>20</v>
@@ -14471,9 +14474,9 @@
       <c r="U57" s="17"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="64"/>
+      <c r="A58" s="61"/>
       <c r="B58" s="35" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C58" s="15" t="s">
         <v>43</v>
@@ -14506,9 +14509,9 @@
       <c r="U58" s="17"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="65"/>
+      <c r="A59" s="62"/>
       <c r="B59" s="35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>47</v>
@@ -14533,11 +14536,11 @@
       <c r="U59" s="17"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="60">
+      <c r="A60" s="57">
         <v>9</v>
       </c>
       <c r="B60" s="37" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>15</v>
@@ -14578,9 +14581,9 @@
       <c r="U60" s="9"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="61"/>
+      <c r="A61" s="58"/>
       <c r="B61" s="37" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>25</v>
@@ -14602,7 +14605,7 @@
         <v>41</v>
       </c>
       <c r="L61" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>40</v>
@@ -14611,7 +14614,7 @@
         <v>41</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P61" s="6"/>
       <c r="Q61" s="8"/>
@@ -14621,9 +14624,9 @@
       <c r="U61" s="9"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="61"/>
+      <c r="A62" s="58"/>
       <c r="B62" s="37" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>29</v>
@@ -14632,19 +14635,19 @@
         <v>26</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J62" s="6" t="s">
         <v>19</v>
@@ -14676,9 +14679,9 @@
       </c>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="61"/>
+      <c r="A63" s="58"/>
       <c r="B63" s="37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>34</v>
@@ -14700,7 +14703,7 @@
         <v>50</v>
       </c>
       <c r="L63" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>49</v>
@@ -14709,7 +14712,7 @@
         <v>50</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P63" s="6"/>
       <c r="Q63" s="8"/>
@@ -14719,9 +14722,9 @@
       <c r="U63" s="32"/>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="61"/>
+      <c r="A64" s="58"/>
       <c r="B64" s="37" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>38</v>
@@ -14733,7 +14736,7 @@
         <v>41</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G64" s="6" t="s">
         <v>40</v>
@@ -14742,7 +14745,7 @@
         <v>41</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J64" s="6" t="s">
         <v>20</v>
@@ -14762,9 +14765,9 @@
       <c r="U64" s="32"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="61"/>
+      <c r="A65" s="58"/>
       <c r="B65" s="37" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>43</v>
@@ -14797,9 +14800,9 @@
       <c r="U65" s="32"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="62"/>
+      <c r="A66" s="59"/>
       <c r="B66" s="37" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C66" s="7" t="s">
         <v>47</v>
@@ -14824,11 +14827,11 @@
       <c r="U66" s="32"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="63">
+      <c r="A67" s="60">
         <v>10</v>
       </c>
       <c r="B67" s="35" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>15</v>
@@ -14869,9 +14872,9 @@
       <c r="U67" s="33"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="64"/>
+      <c r="A68" s="61"/>
       <c r="B68" s="35" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C68" s="15" t="s">
         <v>25</v>
@@ -14893,7 +14896,7 @@
         <v>41</v>
       </c>
       <c r="L68" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M68" s="14" t="s">
         <v>40</v>
@@ -14902,7 +14905,7 @@
         <v>41</v>
       </c>
       <c r="O68" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P68" s="14"/>
       <c r="Q68" s="16"/>
@@ -14912,9 +14915,9 @@
       <c r="U68" s="33"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="64"/>
+      <c r="A69" s="61"/>
       <c r="B69" s="35" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C69" s="15" t="s">
         <v>29</v>
@@ -14923,19 +14926,19 @@
         <v>26</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F69" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G69" s="14" t="s">
         <v>26</v>
       </c>
       <c r="H69" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I69" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J69" s="14" t="s">
         <v>19</v>
@@ -14955,9 +14958,9 @@
       <c r="U69" s="33"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="64"/>
+      <c r="A70" s="61"/>
       <c r="B70" s="35" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C70" s="15" t="s">
         <v>34</v>
@@ -14979,7 +14982,7 @@
         <v>50</v>
       </c>
       <c r="L70" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M70" s="14" t="s">
         <v>49</v>
@@ -14988,7 +14991,7 @@
         <v>50</v>
       </c>
       <c r="O70" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P70" s="14"/>
       <c r="Q70" s="16"/>
@@ -14998,9 +15001,9 @@
       <c r="U70" s="33"/>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="64"/>
+      <c r="A71" s="61"/>
       <c r="B71" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C71" s="15" t="s">
         <v>38</v>
@@ -15012,7 +15015,7 @@
         <v>41</v>
       </c>
       <c r="F71" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G71" s="14" t="s">
         <v>45</v>
@@ -15021,7 +15024,7 @@
         <v>41</v>
       </c>
       <c r="I71" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J71" s="14" t="s">
         <v>20</v>
@@ -15041,9 +15044,9 @@
       <c r="U71" s="33"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="64"/>
+      <c r="A72" s="61"/>
       <c r="B72" s="35" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C72" s="15" t="s">
         <v>43</v>
@@ -15068,9 +15071,9 @@
       <c r="U72" s="33"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="65"/>
+      <c r="A73" s="62"/>
       <c r="B73" s="35" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C73" s="15" t="s">
         <v>47</v>
@@ -15095,11 +15098,11 @@
       <c r="U73" s="33"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="60">
+      <c r="A74" s="57">
         <v>11</v>
       </c>
       <c r="B74" s="37" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C74" s="7" t="s">
         <v>15</v>
@@ -15140,9 +15143,9 @@
       <c r="U74" s="32"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="61"/>
+      <c r="A75" s="58"/>
       <c r="B75" s="37" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C75" s="7" t="s">
         <v>25</v>
@@ -15164,7 +15167,7 @@
         <v>41</v>
       </c>
       <c r="L75" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="M75" s="6" t="s">
         <v>40</v>
@@ -15173,7 +15176,7 @@
         <v>41</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="P75" s="6"/>
       <c r="Q75" s="8"/>
@@ -15183,9 +15186,9 @@
       <c r="U75" s="32"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="61"/>
+      <c r="A76" s="58"/>
       <c r="B76" s="37" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C76" s="7" t="s">
         <v>29</v>
@@ -15194,19 +15197,19 @@
         <v>26</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J76" s="6" t="s">
         <v>19</v>
@@ -15238,9 +15241,9 @@
       </c>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="61"/>
+      <c r="A77" s="58"/>
       <c r="B77" s="37" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C77" s="7" t="s">
         <v>34</v>
@@ -15262,7 +15265,7 @@
         <v>50</v>
       </c>
       <c r="L77" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M77" s="6" t="s">
         <v>49</v>
@@ -15271,7 +15274,7 @@
         <v>50</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P77" s="6"/>
       <c r="Q77" s="8"/>
@@ -15281,9 +15284,9 @@
       <c r="U77" s="9"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="61"/>
+      <c r="A78" s="58"/>
       <c r="B78" s="37" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C78" s="7" t="s">
         <v>38</v>
@@ -15295,7 +15298,7 @@
         <v>41</v>
       </c>
       <c r="F78" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G78" s="6" t="s">
         <v>40</v>
@@ -15304,7 +15307,7 @@
         <v>41</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J78" s="6" t="s">
         <v>20</v>
@@ -15324,9 +15327,9 @@
       <c r="U78" s="9"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="61"/>
+      <c r="A79" s="58"/>
       <c r="B79" s="37" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C79" s="7" t="s">
         <v>43</v>
@@ -15351,9 +15354,9 @@
       <c r="U79" s="9"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="62"/>
+      <c r="A80" s="59"/>
       <c r="B80" s="37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C80" s="7" t="s">
         <v>47</v>
@@ -15378,11 +15381,11 @@
       <c r="U80" s="9"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="63">
+      <c r="A81" s="60">
         <v>12</v>
       </c>
       <c r="B81" s="35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C81" s="15" t="s">
         <v>15</v>
@@ -15423,9 +15426,9 @@
       <c r="U81" s="17"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="64"/>
+      <c r="A82" s="61"/>
       <c r="B82" s="35" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C82" s="15" t="s">
         <v>25</v>
@@ -15454,9 +15457,9 @@
       <c r="U82" s="17"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="64"/>
+      <c r="A83" s="61"/>
       <c r="B83" s="35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C83" s="15" t="s">
         <v>29</v>
@@ -15465,19 +15468,19 @@
         <v>26</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F83" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G83" s="14" t="s">
         <v>26</v>
       </c>
       <c r="H83" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I83" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J83" s="14" t="s">
         <v>19</v>
@@ -15490,28 +15493,28 @@
       <c r="N83" s="16"/>
       <c r="O83" s="17"/>
       <c r="P83" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q83" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R83" s="17" t="s">
         <v>55</v>
       </c>
       <c r="S83" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T83" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U83" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="64"/>
+      <c r="A84" s="61"/>
       <c r="B84" s="35" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C84" s="15" t="s">
         <v>34</v>
@@ -15533,7 +15536,7 @@
         <v>50</v>
       </c>
       <c r="L84" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M84" s="14" t="s">
         <v>49</v>
@@ -15542,7 +15545,7 @@
         <v>50</v>
       </c>
       <c r="O84" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P84" s="14"/>
       <c r="Q84" s="16"/>
@@ -15552,9 +15555,9 @@
       <c r="U84" s="17"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="64"/>
+      <c r="A85" s="61"/>
       <c r="B85" s="35" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C85" s="15" t="s">
         <v>38</v>
@@ -15566,7 +15569,7 @@
         <v>41</v>
       </c>
       <c r="F85" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G85" s="14" t="s">
         <v>45</v>
@@ -15575,7 +15578,7 @@
         <v>41</v>
       </c>
       <c r="I85" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J85" s="14" t="s">
         <v>20</v>
@@ -15595,9 +15598,9 @@
       <c r="U85" s="17"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="64"/>
+      <c r="A86" s="61"/>
       <c r="B86" s="35" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C86" s="15" t="s">
         <v>43</v>
@@ -15630,9 +15633,9 @@
       <c r="U86" s="17"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="65"/>
+      <c r="A87" s="62"/>
       <c r="B87" s="35" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C87" s="15" t="s">
         <v>47</v>
@@ -15657,11 +15660,11 @@
       <c r="U87" s="17"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="60">
+      <c r="A88" s="57">
         <v>13</v>
       </c>
       <c r="B88" s="37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C88" s="7" t="s">
         <v>15</v>
@@ -15702,9 +15705,9 @@
       <c r="U88" s="9"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="61"/>
+      <c r="A89" s="58"/>
       <c r="B89" s="37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C89" s="7" t="s">
         <v>25</v>
@@ -15733,9 +15736,9 @@
       <c r="U89" s="9"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="61"/>
+      <c r="A90" s="58"/>
       <c r="B90" s="37" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C90" s="7" t="s">
         <v>29</v>
@@ -15744,19 +15747,19 @@
         <v>26</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F90" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I90" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J90" s="6" t="s">
         <v>19</v>
@@ -15769,28 +15772,28 @@
       <c r="N90" s="8"/>
       <c r="O90" s="9"/>
       <c r="P90" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q90" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R90" s="9" t="s">
         <v>55</v>
       </c>
       <c r="S90" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T90" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U90" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="61"/>
+      <c r="A91" s="58"/>
       <c r="B91" s="37" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C91" s="7" t="s">
         <v>34</v>
@@ -15812,7 +15815,7 @@
         <v>50</v>
       </c>
       <c r="L91" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M91" s="6" t="s">
         <v>49</v>
@@ -15821,7 +15824,7 @@
         <v>50</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P91" s="6"/>
       <c r="Q91" s="8"/>
@@ -15831,9 +15834,9 @@
       <c r="U91" s="9"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="61"/>
+      <c r="A92" s="58"/>
       <c r="B92" s="37" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C92" s="7" t="s">
         <v>38</v>
@@ -15845,7 +15848,7 @@
         <v>41</v>
       </c>
       <c r="F92" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G92" s="6" t="s">
         <v>40</v>
@@ -15854,7 +15857,7 @@
         <v>41</v>
       </c>
       <c r="I92" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J92" s="6" t="s">
         <v>20</v>
@@ -15874,9 +15877,9 @@
       <c r="U92" s="9"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="61"/>
+      <c r="A93" s="58"/>
       <c r="B93" s="37" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C93" s="7" t="s">
         <v>43</v>
@@ -15909,9 +15912,9 @@
       <c r="U93" s="9"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="62"/>
+      <c r="A94" s="59"/>
       <c r="B94" s="37" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C94" s="7" t="s">
         <v>47</v>
@@ -15936,11 +15939,11 @@
       <c r="U94" s="9"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="63">
+      <c r="A95" s="60">
         <v>14</v>
       </c>
       <c r="B95" s="35" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C95" s="15" t="s">
         <v>15</v>
@@ -15981,9 +15984,9 @@
       <c r="U95" s="17"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="64"/>
+      <c r="A96" s="61"/>
       <c r="B96" s="35" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C96" s="15" t="s">
         <v>25</v>
@@ -16012,9 +16015,9 @@
       <c r="U96" s="17"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="64"/>
+      <c r="A97" s="61"/>
       <c r="B97" s="35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C97" s="15" t="s">
         <v>29</v>
@@ -16023,19 +16026,19 @@
         <v>26</v>
       </c>
       <c r="E97" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F97" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G97" s="14" t="s">
         <v>26</v>
       </c>
       <c r="H97" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I97" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J97" s="14" t="s">
         <v>19</v>
@@ -16048,28 +16051,28 @@
       <c r="N97" s="16"/>
       <c r="O97" s="17"/>
       <c r="P97" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q97" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R97" s="17" t="s">
         <v>55</v>
       </c>
       <c r="S97" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T97" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U97" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="64"/>
+      <c r="A98" s="61"/>
       <c r="B98" s="35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C98" s="15" t="s">
         <v>34</v>
@@ -16091,7 +16094,7 @@
         <v>50</v>
       </c>
       <c r="L98" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M98" s="14" t="s">
         <v>49</v>
@@ -16100,7 +16103,7 @@
         <v>50</v>
       </c>
       <c r="O98" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P98" s="14"/>
       <c r="Q98" s="16"/>
@@ -16110,9 +16113,9 @@
       <c r="U98" s="17"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="64"/>
+      <c r="A99" s="61"/>
       <c r="B99" s="35" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C99" s="15" t="s">
         <v>38</v>
@@ -16124,7 +16127,7 @@
         <v>41</v>
       </c>
       <c r="F99" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G99" s="14" t="s">
         <v>45</v>
@@ -16133,7 +16136,7 @@
         <v>41</v>
       </c>
       <c r="I99" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J99" s="14" t="s">
         <v>20</v>
@@ -16153,9 +16156,9 @@
       <c r="U99" s="17"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="64"/>
+      <c r="A100" s="61"/>
       <c r="B100" s="35" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C100" s="15" t="s">
         <v>43</v>
@@ -16180,9 +16183,9 @@
       <c r="U100" s="17"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="65"/>
+      <c r="A101" s="62"/>
       <c r="B101" s="35" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C101" s="15" t="s">
         <v>47</v>
@@ -16207,11 +16210,11 @@
       <c r="U101" s="17"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="60">
+      <c r="A102" s="57">
         <v>15</v>
       </c>
       <c r="B102" s="37" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C102" s="7" t="s">
         <v>15</v>
@@ -16252,9 +16255,9 @@
       <c r="U102" s="9"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="61"/>
+      <c r="A103" s="58"/>
       <c r="B103" s="37" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C103" s="7" t="s">
         <v>25</v>
@@ -16283,9 +16286,9 @@
       <c r="U103" s="9"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="61"/>
+      <c r="A104" s="58"/>
       <c r="B104" s="37" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C104" s="7" t="s">
         <v>29</v>
@@ -16294,19 +16297,19 @@
         <v>26</v>
       </c>
       <c r="E104" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F104" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I104" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J104" s="6" t="s">
         <v>19</v>
@@ -16319,28 +16322,28 @@
       <c r="N104" s="8"/>
       <c r="O104" s="9"/>
       <c r="P104" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q104" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R104" s="9" t="s">
         <v>55</v>
       </c>
       <c r="S104" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T104" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U104" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="61"/>
+      <c r="A105" s="58"/>
       <c r="B105" s="37" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C105" s="7" t="s">
         <v>34</v>
@@ -16362,7 +16365,7 @@
         <v>50</v>
       </c>
       <c r="L105" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M105" s="6" t="s">
         <v>49</v>
@@ -16371,7 +16374,7 @@
         <v>50</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P105" s="6"/>
       <c r="Q105" s="8"/>
@@ -16381,9 +16384,9 @@
       <c r="U105" s="9"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="61"/>
+      <c r="A106" s="58"/>
       <c r="B106" s="37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C106" s="7" t="s">
         <v>38</v>
@@ -16395,7 +16398,7 @@
         <v>41</v>
       </c>
       <c r="F106" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G106" s="6" t="s">
         <v>40</v>
@@ -16404,7 +16407,7 @@
         <v>41</v>
       </c>
       <c r="I106" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J106" s="6" t="s">
         <v>20</v>
@@ -16424,9 +16427,9 @@
       <c r="U106" s="9"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="61"/>
+      <c r="A107" s="58"/>
       <c r="B107" s="37" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C107" s="7" t="s">
         <v>43</v>
@@ -16459,9 +16462,9 @@
       <c r="U107" s="9"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="62"/>
+      <c r="A108" s="59"/>
       <c r="B108" s="37" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C108" s="7" t="s">
         <v>47</v>
@@ -16486,11 +16489,11 @@
       <c r="U108" s="9"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="63">
+      <c r="A109" s="60">
         <v>16</v>
       </c>
       <c r="B109" s="35" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C109" s="15" t="s">
         <v>15</v>
@@ -16531,9 +16534,9 @@
       <c r="U109" s="33"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="64"/>
+      <c r="A110" s="61"/>
       <c r="B110" s="35" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C110" s="15" t="s">
         <v>25</v>
@@ -16562,9 +16565,9 @@
       <c r="U110" s="33"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="64"/>
+      <c r="A111" s="61"/>
       <c r="B111" s="35" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C111" s="15" t="s">
         <v>29</v>
@@ -16573,19 +16576,19 @@
         <v>26</v>
       </c>
       <c r="E111" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F111" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G111" s="14" t="s">
         <v>26</v>
       </c>
       <c r="H111" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I111" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J111" s="14" t="s">
         <v>19</v>
@@ -16598,28 +16601,28 @@
       <c r="N111" s="16"/>
       <c r="O111" s="17"/>
       <c r="P111" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q111" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R111" s="17" t="s">
         <v>55</v>
       </c>
       <c r="S111" s="14" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T111" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U111" s="17" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="64"/>
+      <c r="A112" s="61"/>
       <c r="B112" s="35" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C112" s="15" t="s">
         <v>34</v>
@@ -16641,7 +16644,7 @@
         <v>50</v>
       </c>
       <c r="L112" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M112" s="14" t="s">
         <v>49</v>
@@ -16650,7 +16653,7 @@
         <v>50</v>
       </c>
       <c r="O112" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P112" s="14"/>
       <c r="Q112" s="16"/>
@@ -16660,9 +16663,9 @@
       <c r="U112" s="33"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="64"/>
+      <c r="A113" s="61"/>
       <c r="B113" s="35" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C113" s="15" t="s">
         <v>38</v>
@@ -16674,7 +16677,7 @@
         <v>41</v>
       </c>
       <c r="F113" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G113" s="14" t="s">
         <v>45</v>
@@ -16683,7 +16686,7 @@
         <v>41</v>
       </c>
       <c r="I113" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J113" s="14" t="s">
         <v>20</v>
@@ -16703,9 +16706,9 @@
       <c r="U113" s="33"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="64"/>
+      <c r="A114" s="61"/>
       <c r="B114" s="35" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C114" s="15" t="s">
         <v>43</v>
@@ -16730,9 +16733,9 @@
       <c r="U114" s="33"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="65"/>
+      <c r="A115" s="62"/>
       <c r="B115" s="35" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C115" s="15" t="s">
         <v>47</v>
@@ -16757,11 +16760,11 @@
       <c r="U115" s="33"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="60">
+      <c r="A116" s="57">
         <v>17</v>
       </c>
       <c r="B116" s="37" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C116" s="7" t="s">
         <v>15</v>
@@ -16788,9 +16791,9 @@
       <c r="U116" s="9"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="61"/>
+      <c r="A117" s="58"/>
       <c r="B117" s="37" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C117" s="7" t="s">
         <v>25</v>
@@ -16817,9 +16820,9 @@
       <c r="U117" s="9"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="61"/>
+      <c r="A118" s="58"/>
       <c r="B118" s="37" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C118" s="7" t="s">
         <v>29</v>
@@ -16828,19 +16831,19 @@
         <v>26</v>
       </c>
       <c r="E118" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F118" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="H118" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="I118" s="9" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J118" s="6"/>
       <c r="K118" s="8"/>
@@ -16851,28 +16854,28 @@
       <c r="N118" s="8"/>
       <c r="O118" s="9"/>
       <c r="P118" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Q118" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="R118" s="9" t="s">
         <v>55</v>
       </c>
       <c r="S118" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="T118" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="U118" s="9" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="61"/>
+      <c r="A119" s="58"/>
       <c r="B119" s="37" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C119" s="7" t="s">
         <v>34</v>
@@ -16892,7 +16895,7 @@
         <v>50</v>
       </c>
       <c r="L119" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M119" s="6" t="s">
         <v>49</v>
@@ -16901,7 +16904,7 @@
         <v>50</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P119" s="6"/>
       <c r="Q119" s="8"/>
@@ -16911,9 +16914,9 @@
       <c r="U119" s="9"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="61"/>
+      <c r="A120" s="58"/>
       <c r="B120" s="37" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C120" s="7" t="s">
         <v>38</v>
@@ -16925,7 +16928,7 @@
         <v>41</v>
       </c>
       <c r="F120" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G120" s="6" t="s">
         <v>40</v>
@@ -16934,7 +16937,7 @@
         <v>41</v>
       </c>
       <c r="I120" s="9" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J120" s="6" t="s">
         <v>20</v>
@@ -16954,9 +16957,9 @@
       <c r="U120" s="9"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="61"/>
+      <c r="A121" s="58"/>
       <c r="B121" s="37" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C121" s="7" t="s">
         <v>43</v>
@@ -16981,9 +16984,9 @@
       <c r="U121" s="9"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="62"/>
+      <c r="A122" s="59"/>
       <c r="B122" s="37" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C122" s="7" t="s">
         <v>47</v>
@@ -17008,413 +17011,393 @@
       <c r="U122" s="9"/>
     </row>
     <row r="123" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="63">
+      <c r="A123" s="60">
         <v>18</v>
       </c>
       <c r="B123" s="35" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C123" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D123" s="72" t="s">
-        <v>171</v>
-      </c>
-      <c r="E123" s="73"/>
-      <c r="F123" s="73"/>
-      <c r="G123" s="73"/>
-      <c r="H123" s="73"/>
-      <c r="I123" s="73"/>
-      <c r="J123" s="73"/>
-      <c r="K123" s="73"/>
-      <c r="L123" s="73"/>
-      <c r="M123" s="73"/>
-      <c r="N123" s="73"/>
-      <c r="O123" s="73"/>
-      <c r="P123" s="73"/>
-      <c r="Q123" s="73"/>
-      <c r="R123" s="73"/>
-      <c r="S123" s="73"/>
-      <c r="T123" s="73"/>
-      <c r="U123" s="74"/>
+      <c r="D123" s="48" t="s">
+        <v>172</v>
+      </c>
+      <c r="E123" s="49"/>
+      <c r="F123" s="49"/>
+      <c r="G123" s="49"/>
+      <c r="H123" s="49"/>
+      <c r="I123" s="49"/>
+      <c r="J123" s="49"/>
+      <c r="K123" s="49"/>
+      <c r="L123" s="49"/>
+      <c r="M123" s="49"/>
+      <c r="N123" s="49"/>
+      <c r="O123" s="49"/>
+      <c r="P123" s="49"/>
+      <c r="Q123" s="49"/>
+      <c r="R123" s="49"/>
+      <c r="S123" s="49"/>
+      <c r="T123" s="49"/>
+      <c r="U123" s="50"/>
     </row>
     <row r="124" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="64"/>
+      <c r="A124" s="61"/>
       <c r="B124" s="35" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C124" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="D124" s="75"/>
-      <c r="E124" s="76"/>
-      <c r="F124" s="76"/>
-      <c r="G124" s="76"/>
-      <c r="H124" s="76"/>
-      <c r="I124" s="76"/>
-      <c r="J124" s="76"/>
-      <c r="K124" s="76"/>
-      <c r="L124" s="76"/>
-      <c r="M124" s="76"/>
-      <c r="N124" s="76"/>
-      <c r="O124" s="76"/>
-      <c r="P124" s="76"/>
-      <c r="Q124" s="76"/>
-      <c r="R124" s="76"/>
-      <c r="S124" s="76"/>
-      <c r="T124" s="76"/>
-      <c r="U124" s="77"/>
+      <c r="D124" s="51"/>
+      <c r="E124" s="52"/>
+      <c r="F124" s="52"/>
+      <c r="G124" s="52"/>
+      <c r="H124" s="52"/>
+      <c r="I124" s="52"/>
+      <c r="J124" s="52"/>
+      <c r="K124" s="52"/>
+      <c r="L124" s="52"/>
+      <c r="M124" s="52"/>
+      <c r="N124" s="52"/>
+      <c r="O124" s="52"/>
+      <c r="P124" s="52"/>
+      <c r="Q124" s="52"/>
+      <c r="R124" s="52"/>
+      <c r="S124" s="52"/>
+      <c r="T124" s="52"/>
+      <c r="U124" s="53"/>
     </row>
     <row r="125" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="64"/>
+      <c r="A125" s="61"/>
       <c r="B125" s="35" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C125" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="D125" s="75"/>
-      <c r="E125" s="76"/>
-      <c r="F125" s="76"/>
-      <c r="G125" s="76"/>
-      <c r="H125" s="76"/>
-      <c r="I125" s="76"/>
-      <c r="J125" s="76"/>
-      <c r="K125" s="76"/>
-      <c r="L125" s="76"/>
-      <c r="M125" s="76"/>
-      <c r="N125" s="76"/>
-      <c r="O125" s="76"/>
-      <c r="P125" s="76"/>
-      <c r="Q125" s="76"/>
-      <c r="R125" s="76"/>
-      <c r="S125" s="76"/>
-      <c r="T125" s="76"/>
-      <c r="U125" s="77"/>
+      <c r="D125" s="51"/>
+      <c r="E125" s="52"/>
+      <c r="F125" s="52"/>
+      <c r="G125" s="52"/>
+      <c r="H125" s="52"/>
+      <c r="I125" s="52"/>
+      <c r="J125" s="52"/>
+      <c r="K125" s="52"/>
+      <c r="L125" s="52"/>
+      <c r="M125" s="52"/>
+      <c r="N125" s="52"/>
+      <c r="O125" s="52"/>
+      <c r="P125" s="52"/>
+      <c r="Q125" s="52"/>
+      <c r="R125" s="52"/>
+      <c r="S125" s="52"/>
+      <c r="T125" s="52"/>
+      <c r="U125" s="53"/>
     </row>
     <row r="126" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="64"/>
+      <c r="A126" s="61"/>
       <c r="B126" s="35" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C126" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="D126" s="75"/>
-      <c r="E126" s="76"/>
-      <c r="F126" s="76"/>
-      <c r="G126" s="76"/>
-      <c r="H126" s="76"/>
-      <c r="I126" s="76"/>
-      <c r="J126" s="76"/>
-      <c r="K126" s="76"/>
-      <c r="L126" s="76"/>
-      <c r="M126" s="76"/>
-      <c r="N126" s="76"/>
-      <c r="O126" s="76"/>
-      <c r="P126" s="76"/>
-      <c r="Q126" s="76"/>
-      <c r="R126" s="76"/>
-      <c r="S126" s="76"/>
-      <c r="T126" s="76"/>
-      <c r="U126" s="77"/>
+      <c r="D126" s="51"/>
+      <c r="E126" s="52"/>
+      <c r="F126" s="52"/>
+      <c r="G126" s="52"/>
+      <c r="H126" s="52"/>
+      <c r="I126" s="52"/>
+      <c r="J126" s="52"/>
+      <c r="K126" s="52"/>
+      <c r="L126" s="52"/>
+      <c r="M126" s="52"/>
+      <c r="N126" s="52"/>
+      <c r="O126" s="52"/>
+      <c r="P126" s="52"/>
+      <c r="Q126" s="52"/>
+      <c r="R126" s="52"/>
+      <c r="S126" s="52"/>
+      <c r="T126" s="52"/>
+      <c r="U126" s="53"/>
     </row>
     <row r="127" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="64"/>
+      <c r="A127" s="61"/>
       <c r="B127" s="34" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C127" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D127" s="75"/>
-      <c r="E127" s="76"/>
-      <c r="F127" s="76"/>
-      <c r="G127" s="76"/>
-      <c r="H127" s="76"/>
-      <c r="I127" s="76"/>
-      <c r="J127" s="76"/>
-      <c r="K127" s="76"/>
-      <c r="L127" s="76"/>
-      <c r="M127" s="76"/>
-      <c r="N127" s="76"/>
-      <c r="O127" s="76"/>
-      <c r="P127" s="76"/>
-      <c r="Q127" s="76"/>
-      <c r="R127" s="76"/>
-      <c r="S127" s="76"/>
-      <c r="T127" s="76"/>
-      <c r="U127" s="77"/>
+      <c r="D127" s="51"/>
+      <c r="E127" s="52"/>
+      <c r="F127" s="52"/>
+      <c r="G127" s="52"/>
+      <c r="H127" s="52"/>
+      <c r="I127" s="52"/>
+      <c r="J127" s="52"/>
+      <c r="K127" s="52"/>
+      <c r="L127" s="52"/>
+      <c r="M127" s="52"/>
+      <c r="N127" s="52"/>
+      <c r="O127" s="52"/>
+      <c r="P127" s="52"/>
+      <c r="Q127" s="52"/>
+      <c r="R127" s="52"/>
+      <c r="S127" s="52"/>
+      <c r="T127" s="52"/>
+      <c r="U127" s="53"/>
     </row>
     <row r="128" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="64"/>
+      <c r="A128" s="61"/>
       <c r="B128" s="35" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C128" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D128" s="75"/>
-      <c r="E128" s="76"/>
-      <c r="F128" s="76"/>
-      <c r="G128" s="76"/>
-      <c r="H128" s="76"/>
-      <c r="I128" s="76"/>
-      <c r="J128" s="76"/>
-      <c r="K128" s="76"/>
-      <c r="L128" s="76"/>
-      <c r="M128" s="76"/>
-      <c r="N128" s="76"/>
-      <c r="O128" s="76"/>
-      <c r="P128" s="76"/>
-      <c r="Q128" s="76"/>
-      <c r="R128" s="76"/>
-      <c r="S128" s="76"/>
-      <c r="T128" s="76"/>
-      <c r="U128" s="77"/>
+      <c r="D128" s="51"/>
+      <c r="E128" s="52"/>
+      <c r="F128" s="52"/>
+      <c r="G128" s="52"/>
+      <c r="H128" s="52"/>
+      <c r="I128" s="52"/>
+      <c r="J128" s="52"/>
+      <c r="K128" s="52"/>
+      <c r="L128" s="52"/>
+      <c r="M128" s="52"/>
+      <c r="N128" s="52"/>
+      <c r="O128" s="52"/>
+      <c r="P128" s="52"/>
+      <c r="Q128" s="52"/>
+      <c r="R128" s="52"/>
+      <c r="S128" s="52"/>
+      <c r="T128" s="52"/>
+      <c r="U128" s="53"/>
     </row>
     <row r="129" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="65"/>
+      <c r="A129" s="62"/>
       <c r="B129" s="35" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C129" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D129" s="75"/>
-      <c r="E129" s="76"/>
-      <c r="F129" s="76"/>
-      <c r="G129" s="76"/>
-      <c r="H129" s="76"/>
-      <c r="I129" s="76"/>
-      <c r="J129" s="76"/>
-      <c r="K129" s="76"/>
-      <c r="L129" s="76"/>
-      <c r="M129" s="76"/>
-      <c r="N129" s="76"/>
-      <c r="O129" s="76"/>
-      <c r="P129" s="76"/>
-      <c r="Q129" s="76"/>
-      <c r="R129" s="76"/>
-      <c r="S129" s="76"/>
-      <c r="T129" s="76"/>
-      <c r="U129" s="77"/>
+      <c r="D129" s="51"/>
+      <c r="E129" s="52"/>
+      <c r="F129" s="52"/>
+      <c r="G129" s="52"/>
+      <c r="H129" s="52"/>
+      <c r="I129" s="52"/>
+      <c r="J129" s="52"/>
+      <c r="K129" s="52"/>
+      <c r="L129" s="52"/>
+      <c r="M129" s="52"/>
+      <c r="N129" s="52"/>
+      <c r="O129" s="52"/>
+      <c r="P129" s="52"/>
+      <c r="Q129" s="52"/>
+      <c r="R129" s="52"/>
+      <c r="S129" s="52"/>
+      <c r="T129" s="52"/>
+      <c r="U129" s="53"/>
     </row>
     <row r="130" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="60">
+      <c r="A130" s="57">
         <v>19</v>
       </c>
       <c r="B130" s="37" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C130" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D130" s="75"/>
-      <c r="E130" s="76"/>
-      <c r="F130" s="76"/>
-      <c r="G130" s="76"/>
-      <c r="H130" s="76"/>
-      <c r="I130" s="76"/>
-      <c r="J130" s="76"/>
-      <c r="K130" s="76"/>
-      <c r="L130" s="76"/>
-      <c r="M130" s="76"/>
-      <c r="N130" s="76"/>
-      <c r="O130" s="76"/>
-      <c r="P130" s="76"/>
-      <c r="Q130" s="76"/>
-      <c r="R130" s="76"/>
-      <c r="S130" s="76"/>
-      <c r="T130" s="76"/>
-      <c r="U130" s="77"/>
+      <c r="D130" s="51"/>
+      <c r="E130" s="52"/>
+      <c r="F130" s="52"/>
+      <c r="G130" s="52"/>
+      <c r="H130" s="52"/>
+      <c r="I130" s="52"/>
+      <c r="J130" s="52"/>
+      <c r="K130" s="52"/>
+      <c r="L130" s="52"/>
+      <c r="M130" s="52"/>
+      <c r="N130" s="52"/>
+      <c r="O130" s="52"/>
+      <c r="P130" s="52"/>
+      <c r="Q130" s="52"/>
+      <c r="R130" s="52"/>
+      <c r="S130" s="52"/>
+      <c r="T130" s="52"/>
+      <c r="U130" s="53"/>
     </row>
     <row r="131" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="61"/>
+      <c r="A131" s="58"/>
       <c r="B131" s="37" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C131" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D131" s="75"/>
-      <c r="E131" s="76"/>
-      <c r="F131" s="76"/>
-      <c r="G131" s="76"/>
-      <c r="H131" s="76"/>
-      <c r="I131" s="76"/>
-      <c r="J131" s="76"/>
-      <c r="K131" s="76"/>
-      <c r="L131" s="76"/>
-      <c r="M131" s="76"/>
-      <c r="N131" s="76"/>
-      <c r="O131" s="76"/>
-      <c r="P131" s="76"/>
-      <c r="Q131" s="76"/>
-      <c r="R131" s="76"/>
-      <c r="S131" s="76"/>
-      <c r="T131" s="76"/>
-      <c r="U131" s="77"/>
+      <c r="D131" s="51"/>
+      <c r="E131" s="52"/>
+      <c r="F131" s="52"/>
+      <c r="G131" s="52"/>
+      <c r="H131" s="52"/>
+      <c r="I131" s="52"/>
+      <c r="J131" s="52"/>
+      <c r="K131" s="52"/>
+      <c r="L131" s="52"/>
+      <c r="M131" s="52"/>
+      <c r="N131" s="52"/>
+      <c r="O131" s="52"/>
+      <c r="P131" s="52"/>
+      <c r="Q131" s="52"/>
+      <c r="R131" s="52"/>
+      <c r="S131" s="52"/>
+      <c r="T131" s="52"/>
+      <c r="U131" s="53"/>
     </row>
     <row r="132" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="61"/>
+      <c r="A132" s="58"/>
       <c r="B132" s="37" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C132" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D132" s="75"/>
-      <c r="E132" s="76"/>
-      <c r="F132" s="76"/>
-      <c r="G132" s="76"/>
-      <c r="H132" s="76"/>
-      <c r="I132" s="76"/>
-      <c r="J132" s="76"/>
-      <c r="K132" s="76"/>
-      <c r="L132" s="76"/>
-      <c r="M132" s="76"/>
-      <c r="N132" s="76"/>
-      <c r="O132" s="76"/>
-      <c r="P132" s="76"/>
-      <c r="Q132" s="76"/>
-      <c r="R132" s="76"/>
-      <c r="S132" s="76"/>
-      <c r="T132" s="76"/>
-      <c r="U132" s="77"/>
+      <c r="D132" s="51"/>
+      <c r="E132" s="52"/>
+      <c r="F132" s="52"/>
+      <c r="G132" s="52"/>
+      <c r="H132" s="52"/>
+      <c r="I132" s="52"/>
+      <c r="J132" s="52"/>
+      <c r="K132" s="52"/>
+      <c r="L132" s="52"/>
+      <c r="M132" s="52"/>
+      <c r="N132" s="52"/>
+      <c r="O132" s="52"/>
+      <c r="P132" s="52"/>
+      <c r="Q132" s="52"/>
+      <c r="R132" s="52"/>
+      <c r="S132" s="52"/>
+      <c r="T132" s="52"/>
+      <c r="U132" s="53"/>
     </row>
     <row r="133" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="61"/>
+      <c r="A133" s="58"/>
       <c r="B133" s="37" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C133" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D133" s="75"/>
-      <c r="E133" s="76"/>
-      <c r="F133" s="76"/>
-      <c r="G133" s="76"/>
-      <c r="H133" s="76"/>
-      <c r="I133" s="76"/>
-      <c r="J133" s="76"/>
-      <c r="K133" s="76"/>
-      <c r="L133" s="76"/>
-      <c r="M133" s="76"/>
-      <c r="N133" s="76"/>
-      <c r="O133" s="76"/>
-      <c r="P133" s="76"/>
-      <c r="Q133" s="76"/>
-      <c r="R133" s="76"/>
-      <c r="S133" s="76"/>
-      <c r="T133" s="76"/>
-      <c r="U133" s="77"/>
+      <c r="D133" s="51"/>
+      <c r="E133" s="52"/>
+      <c r="F133" s="52"/>
+      <c r="G133" s="52"/>
+      <c r="H133" s="52"/>
+      <c r="I133" s="52"/>
+      <c r="J133" s="52"/>
+      <c r="K133" s="52"/>
+      <c r="L133" s="52"/>
+      <c r="M133" s="52"/>
+      <c r="N133" s="52"/>
+      <c r="O133" s="52"/>
+      <c r="P133" s="52"/>
+      <c r="Q133" s="52"/>
+      <c r="R133" s="52"/>
+      <c r="S133" s="52"/>
+      <c r="T133" s="52"/>
+      <c r="U133" s="53"/>
     </row>
     <row r="134" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="61"/>
+      <c r="A134" s="58"/>
       <c r="B134" s="37" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C134" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="D134" s="75"/>
-      <c r="E134" s="76"/>
-      <c r="F134" s="76"/>
-      <c r="G134" s="76"/>
-      <c r="H134" s="76"/>
-      <c r="I134" s="76"/>
-      <c r="J134" s="76"/>
-      <c r="K134" s="76"/>
-      <c r="L134" s="76"/>
-      <c r="M134" s="76"/>
-      <c r="N134" s="76"/>
-      <c r="O134" s="76"/>
-      <c r="P134" s="76"/>
-      <c r="Q134" s="76"/>
-      <c r="R134" s="76"/>
-      <c r="S134" s="76"/>
-      <c r="T134" s="76"/>
-      <c r="U134" s="77"/>
+      <c r="D134" s="51"/>
+      <c r="E134" s="52"/>
+      <c r="F134" s="52"/>
+      <c r="G134" s="52"/>
+      <c r="H134" s="52"/>
+      <c r="I134" s="52"/>
+      <c r="J134" s="52"/>
+      <c r="K134" s="52"/>
+      <c r="L134" s="52"/>
+      <c r="M134" s="52"/>
+      <c r="N134" s="52"/>
+      <c r="O134" s="52"/>
+      <c r="P134" s="52"/>
+      <c r="Q134" s="52"/>
+      <c r="R134" s="52"/>
+      <c r="S134" s="52"/>
+      <c r="T134" s="52"/>
+      <c r="U134" s="53"/>
     </row>
     <row r="135" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="61"/>
+      <c r="A135" s="58"/>
       <c r="B135" s="37" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C135" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D135" s="75"/>
-      <c r="E135" s="76"/>
-      <c r="F135" s="76"/>
-      <c r="G135" s="76"/>
-      <c r="H135" s="76"/>
-      <c r="I135" s="76"/>
-      <c r="J135" s="76"/>
-      <c r="K135" s="76"/>
-      <c r="L135" s="76"/>
-      <c r="M135" s="76"/>
-      <c r="N135" s="76"/>
-      <c r="O135" s="76"/>
-      <c r="P135" s="76"/>
-      <c r="Q135" s="76"/>
-      <c r="R135" s="76"/>
-      <c r="S135" s="76"/>
-      <c r="T135" s="76"/>
-      <c r="U135" s="77"/>
+      <c r="D135" s="51"/>
+      <c r="E135" s="52"/>
+      <c r="F135" s="52"/>
+      <c r="G135" s="52"/>
+      <c r="H135" s="52"/>
+      <c r="I135" s="52"/>
+      <c r="J135" s="52"/>
+      <c r="K135" s="52"/>
+      <c r="L135" s="52"/>
+      <c r="M135" s="52"/>
+      <c r="N135" s="52"/>
+      <c r="O135" s="52"/>
+      <c r="P135" s="52"/>
+      <c r="Q135" s="52"/>
+      <c r="R135" s="52"/>
+      <c r="S135" s="52"/>
+      <c r="T135" s="52"/>
+      <c r="U135" s="53"/>
     </row>
     <row r="136" spans="1:21" s="2" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="62"/>
+      <c r="A136" s="59"/>
       <c r="B136" s="37" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C136" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="D136" s="78"/>
-      <c r="E136" s="79"/>
-      <c r="F136" s="79"/>
-      <c r="G136" s="79"/>
-      <c r="H136" s="79"/>
-      <c r="I136" s="79"/>
-      <c r="J136" s="79"/>
-      <c r="K136" s="79"/>
-      <c r="L136" s="79"/>
-      <c r="M136" s="79"/>
-      <c r="N136" s="79"/>
-      <c r="O136" s="79"/>
-      <c r="P136" s="79"/>
-      <c r="Q136" s="79"/>
-      <c r="R136" s="79"/>
-      <c r="S136" s="79"/>
-      <c r="T136" s="79"/>
-      <c r="U136" s="80"/>
+      <c r="D136" s="54"/>
+      <c r="E136" s="55"/>
+      <c r="F136" s="55"/>
+      <c r="G136" s="55"/>
+      <c r="H136" s="55"/>
+      <c r="I136" s="55"/>
+      <c r="J136" s="55"/>
+      <c r="K136" s="55"/>
+      <c r="L136" s="55"/>
+      <c r="M136" s="55"/>
+      <c r="N136" s="55"/>
+      <c r="O136" s="55"/>
+      <c r="P136" s="55"/>
+      <c r="Q136" s="55"/>
+      <c r="R136" s="55"/>
+      <c r="S136" s="55"/>
+      <c r="T136" s="55"/>
+      <c r="U136" s="56"/>
     </row>
     <row r="137" spans="1:21"/>
     <row r="150"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="D123:U136"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="A81:A87"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="D29:U31"/>
@@ -17431,6 +17414,26 @@
     <mergeCell ref="S3:U3"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="B2:C3"/>
+    <mergeCell ref="D2:F2"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="D123:U136"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A123:A129"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
